--- a/Cobros_Procesadores.xlsx
+++ b/Cobros_Procesadores.xlsx
@@ -156,7 +156,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB328"/>
+  <dimension ref="A1:AO328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -568,8 +568,18 @@
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
-    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -587,14 +597,14 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>CIERRE SEMANAL — RETENIDO NETO AL DOMINGO 23:59</t>
+          <t>CIERRE SEMANAL — para Temporary Restriction (Ventas − Fees = Venta Neta · Collected · Retenido)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Importe neto (venta - comisión - refund) vendido y aún no liquidado en ningún procesador al cierre de cada semana.</t>
+          <t>Por semana ISO y procesador. Venta Neta = Ventas − Fees (ventas limpias de comisiones). Retenido = neto vendido hasta el domingo y aún sin liquidar.</t>
         </is>
       </c>
     </row>
@@ -651,34 +661,44 @@
       </c>
       <c r="L5" s="7" t="n"/>
       <c r="M5" s="7" t="n"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="n"/>
+      <c r="O5" s="7" t="n"/>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>Nuvei</t>
         </is>
       </c>
-      <c r="O5" s="7" t="n"/>
-      <c r="P5" s="7" t="n"/>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>Shift4</t>
-        </is>
-      </c>
+      <c r="Q5" s="7" t="n"/>
       <c r="R5" s="7" t="n"/>
       <c r="S5" s="7" t="n"/>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>Paysafe</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="n"/>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>Shift4</t>
+        </is>
+      </c>
       <c r="V5" s="7" t="n"/>
-      <c r="W5" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="W5" s="7" t="n"/>
       <c r="X5" s="7" t="n"/>
       <c r="Y5" s="7" t="n"/>
+      <c r="Z5" s="6" t="inlineStr">
+        <is>
+          <t>Paysafe</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="n"/>
+      <c r="AB5" s="7" t="n"/>
+      <c r="AC5" s="7" t="n"/>
+      <c r="AD5" s="7" t="n"/>
+      <c r="AE5" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="AF5" s="7" t="n"/>
+      <c r="AG5" s="7" t="n"/>
+      <c r="AH5" s="7" t="n"/>
+      <c r="AI5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -709,75 +729,125 @@
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>Vendido</t>
+          <t>Ventas</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>Cobrado</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
+          <t>Venta Neta</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
           <t>Retenido</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>Vendido</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>Cobrado</t>
-        </is>
-      </c>
       <c r="P6" s="11" t="inlineStr">
         <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="Q6" s="11" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>Venta Neta</t>
+        </is>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
           <t>Retenido</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
-        <is>
-          <t>Vendido</t>
-        </is>
-      </c>
-      <c r="R6" s="11" t="inlineStr">
-        <is>
-          <t>Cobrado</t>
-        </is>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="U6" s="11" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>Venta Neta</t>
+        </is>
+      </c>
+      <c r="X6" s="11" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="Y6" s="11" t="inlineStr">
         <is>
           <t>Retenido</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>Vendido</t>
-        </is>
-      </c>
-      <c r="U6" s="11" t="inlineStr">
-        <is>
-          <t>Cobrado</t>
-        </is>
-      </c>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="Z6" s="11" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="AA6" s="11" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="AB6" s="11" t="inlineStr">
+        <is>
+          <t>Venta Neta</t>
+        </is>
+      </c>
+      <c r="AC6" s="11" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="AD6" s="11" t="inlineStr">
         <is>
           <t>Retenido</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
-        <is>
-          <t>Vendido</t>
-        </is>
-      </c>
-      <c r="X6" s="11" t="inlineStr">
-        <is>
-          <t>Cobrado</t>
-        </is>
-      </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="AE6" s="11" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="AF6" s="11" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="AG6" s="11" t="inlineStr">
+        <is>
+          <t>Venta Neta</t>
+        </is>
+      </c>
+      <c r="AH6" s="11" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="AI6" s="11" t="inlineStr">
         <is>
           <t>Retenido</t>
         </is>
@@ -821,69 +891,109 @@
         </is>
       </c>
       <c r="K7" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA7,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB7)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN7,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO7)</f>
         <v/>
       </c>
       <c r="L7" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA7,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB7)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN7,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO7)</f>
         <v/>
       </c>
       <c r="M7" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB7,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB7)</f>
+        <f>K7-L7</f>
         <v/>
       </c>
       <c r="N7" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA7,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB7)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN7,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO7)</f>
         <v/>
       </c>
       <c r="O7" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA7,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB7)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO7,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO7)</f>
         <v/>
       </c>
       <c r="P7" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB7,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB7)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN7,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO7)</f>
         <v/>
       </c>
       <c r="Q7" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA7,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB7)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN7,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO7)</f>
         <v/>
       </c>
       <c r="R7" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA7,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB7)</f>
+        <f>P7-Q7</f>
         <v/>
       </c>
       <c r="S7" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB7,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB7)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN7,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO7)</f>
         <v/>
       </c>
       <c r="T7" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA7,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB7)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO7,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO7)</f>
         <v/>
       </c>
       <c r="U7" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA7,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB7)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN7,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO7)</f>
         <v/>
       </c>
       <c r="V7" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB7,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB7)</f>
-        <v/>
-      </c>
-      <c r="W7" s="10">
-        <f>K7+N7+Q7+T7</f>
-        <v/>
-      </c>
-      <c r="X7" s="10">
-        <f>L7+O7+R7+U7</f>
-        <v/>
-      </c>
-      <c r="Y7" s="10">
-        <f>M7+P7+S7+V7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN7,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO7)</f>
+        <v/>
+      </c>
+      <c r="W7" s="9">
+        <f>U7-V7</f>
+        <v/>
+      </c>
+      <c r="X7" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN7,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO7)</f>
+        <v/>
+      </c>
+      <c r="Y7" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO7,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO7)</f>
+        <v/>
+      </c>
+      <c r="Z7" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN7,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO7)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN7,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO7)</f>
+        <v/>
+      </c>
+      <c r="AB7" s="9">
+        <f>Z7-AA7</f>
+        <v/>
+      </c>
+      <c r="AC7" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN7,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO7)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO7,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO7)</f>
+        <v/>
+      </c>
+      <c r="AE7" s="10">
+        <f>K7+P7+U7+Z7</f>
+        <v/>
+      </c>
+      <c r="AF7" s="10">
+        <f>L7+Q7+V7+AA7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="10">
+        <f>M7+R7+W7+AB7</f>
+        <v/>
+      </c>
+      <c r="AH7" s="10">
+        <f>N7+S7+X7+AC7</f>
+        <v/>
+      </c>
+      <c r="AI7" s="10">
+        <f>O7+T7+Y7+AD7</f>
+        <v/>
+      </c>
+      <c r="AN7" s="8" t="n">
         <v>45922</v>
       </c>
-      <c r="AB7" s="8" t="n">
+      <c r="AO7" s="8" t="n">
         <v>45928</v>
       </c>
     </row>
@@ -925,69 +1035,109 @@
         </is>
       </c>
       <c r="K8" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA8,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB8)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN8,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO8)</f>
         <v/>
       </c>
       <c r="L8" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA8,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB8)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN8,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO8)</f>
         <v/>
       </c>
       <c r="M8" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB8,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB8)</f>
+        <f>K8-L8</f>
         <v/>
       </c>
       <c r="N8" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA8,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB8)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN8,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO8)</f>
         <v/>
       </c>
       <c r="O8" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA8,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB8)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO8,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO8)</f>
         <v/>
       </c>
       <c r="P8" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB8,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB8)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN8,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO8)</f>
         <v/>
       </c>
       <c r="Q8" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA8,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB8)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN8,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO8)</f>
         <v/>
       </c>
       <c r="R8" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA8,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB8)</f>
+        <f>P8-Q8</f>
         <v/>
       </c>
       <c r="S8" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB8,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB8)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN8,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO8)</f>
         <v/>
       </c>
       <c r="T8" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA8,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB8)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO8,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO8)</f>
         <v/>
       </c>
       <c r="U8" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA8,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB8)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN8,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO8)</f>
         <v/>
       </c>
       <c r="V8" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB8,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB8)</f>
-        <v/>
-      </c>
-      <c r="W8" s="10">
-        <f>K8+N8+Q8+T8</f>
-        <v/>
-      </c>
-      <c r="X8" s="10">
-        <f>L8+O8+R8+U8</f>
-        <v/>
-      </c>
-      <c r="Y8" s="10">
-        <f>M8+P8+S8+V8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN8,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO8)</f>
+        <v/>
+      </c>
+      <c r="W8" s="9">
+        <f>U8-V8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN8,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO8)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO8,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO8)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN8,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO8)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN8,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO8)</f>
+        <v/>
+      </c>
+      <c r="AB8" s="9">
+        <f>Z8-AA8</f>
+        <v/>
+      </c>
+      <c r="AC8" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN8,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO8)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO8,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO8)</f>
+        <v/>
+      </c>
+      <c r="AE8" s="10">
+        <f>K8+P8+U8+Z8</f>
+        <v/>
+      </c>
+      <c r="AF8" s="10">
+        <f>L8+Q8+V8+AA8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="10">
+        <f>M8+R8+W8+AB8</f>
+        <v/>
+      </c>
+      <c r="AH8" s="10">
+        <f>N8+S8+X8+AC8</f>
+        <v/>
+      </c>
+      <c r="AI8" s="10">
+        <f>O8+T8+Y8+AD8</f>
+        <v/>
+      </c>
+      <c r="AN8" s="8" t="n">
         <v>45929</v>
       </c>
-      <c r="AB8" s="8" t="n">
+      <c r="AO8" s="8" t="n">
         <v>45935</v>
       </c>
     </row>
@@ -1029,69 +1179,109 @@
         </is>
       </c>
       <c r="K9" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA9,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB9)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN9,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO9)</f>
         <v/>
       </c>
       <c r="L9" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA9,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB9)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN9,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO9)</f>
         <v/>
       </c>
       <c r="M9" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB9,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB9)</f>
+        <f>K9-L9</f>
         <v/>
       </c>
       <c r="N9" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA9,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB9)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN9,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO9)</f>
         <v/>
       </c>
       <c r="O9" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA9,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB9)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO9,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO9)</f>
         <v/>
       </c>
       <c r="P9" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB9,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB9)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN9,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO9)</f>
         <v/>
       </c>
       <c r="Q9" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA9,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB9)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN9,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO9)</f>
         <v/>
       </c>
       <c r="R9" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA9,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB9)</f>
+        <f>P9-Q9</f>
         <v/>
       </c>
       <c r="S9" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB9,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB9)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN9,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO9)</f>
         <v/>
       </c>
       <c r="T9" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA9,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB9)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO9,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO9)</f>
         <v/>
       </c>
       <c r="U9" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA9,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB9)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN9,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO9)</f>
         <v/>
       </c>
       <c r="V9" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB9,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB9)</f>
-        <v/>
-      </c>
-      <c r="W9" s="10">
-        <f>K9+N9+Q9+T9</f>
-        <v/>
-      </c>
-      <c r="X9" s="10">
-        <f>L9+O9+R9+U9</f>
-        <v/>
-      </c>
-      <c r="Y9" s="10">
-        <f>M9+P9+S9+V9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN9,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO9)</f>
+        <v/>
+      </c>
+      <c r="W9" s="9">
+        <f>U9-V9</f>
+        <v/>
+      </c>
+      <c r="X9" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN9,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO9)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO9,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO9)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN9,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO9)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN9,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO9)</f>
+        <v/>
+      </c>
+      <c r="AB9" s="9">
+        <f>Z9-AA9</f>
+        <v/>
+      </c>
+      <c r="AC9" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN9,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO9)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO9,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO9)</f>
+        <v/>
+      </c>
+      <c r="AE9" s="10">
+        <f>K9+P9+U9+Z9</f>
+        <v/>
+      </c>
+      <c r="AF9" s="10">
+        <f>L9+Q9+V9+AA9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="10">
+        <f>M9+R9+W9+AB9</f>
+        <v/>
+      </c>
+      <c r="AH9" s="10">
+        <f>N9+S9+X9+AC9</f>
+        <v/>
+      </c>
+      <c r="AI9" s="10">
+        <f>O9+T9+Y9+AD9</f>
+        <v/>
+      </c>
+      <c r="AN9" s="8" t="n">
         <v>45936</v>
       </c>
-      <c r="AB9" s="8" t="n">
+      <c r="AO9" s="8" t="n">
         <v>45942</v>
       </c>
     </row>
@@ -1133,69 +1323,109 @@
         </is>
       </c>
       <c r="K10" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA10,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB10)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN10,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO10)</f>
         <v/>
       </c>
       <c r="L10" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA10,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB10)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN10,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO10)</f>
         <v/>
       </c>
       <c r="M10" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB10,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB10)</f>
+        <f>K10-L10</f>
         <v/>
       </c>
       <c r="N10" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA10,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB10)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN10,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO10)</f>
         <v/>
       </c>
       <c r="O10" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA10,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB10)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO10,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO10)</f>
         <v/>
       </c>
       <c r="P10" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB10,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB10)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN10,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO10)</f>
         <v/>
       </c>
       <c r="Q10" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA10,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB10)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN10,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO10)</f>
         <v/>
       </c>
       <c r="R10" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA10,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB10)</f>
+        <f>P10-Q10</f>
         <v/>
       </c>
       <c r="S10" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB10,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB10)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN10,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO10)</f>
         <v/>
       </c>
       <c r="T10" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA10,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB10)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO10,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO10)</f>
         <v/>
       </c>
       <c r="U10" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA10,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB10)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN10,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO10)</f>
         <v/>
       </c>
       <c r="V10" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB10,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB10)</f>
-        <v/>
-      </c>
-      <c r="W10" s="10">
-        <f>K10+N10+Q10+T10</f>
-        <v/>
-      </c>
-      <c r="X10" s="10">
-        <f>L10+O10+R10+U10</f>
-        <v/>
-      </c>
-      <c r="Y10" s="10">
-        <f>M10+P10+S10+V10</f>
-        <v/>
-      </c>
-      <c r="AA10" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN10,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO10)</f>
+        <v/>
+      </c>
+      <c r="W10" s="9">
+        <f>U10-V10</f>
+        <v/>
+      </c>
+      <c r="X10" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN10,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO10)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO10,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO10)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN10,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO10)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN10,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO10)</f>
+        <v/>
+      </c>
+      <c r="AB10" s="9">
+        <f>Z10-AA10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN10,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO10)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO10,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO10)</f>
+        <v/>
+      </c>
+      <c r="AE10" s="10">
+        <f>K10+P10+U10+Z10</f>
+        <v/>
+      </c>
+      <c r="AF10" s="10">
+        <f>L10+Q10+V10+AA10</f>
+        <v/>
+      </c>
+      <c r="AG10" s="10">
+        <f>M10+R10+W10+AB10</f>
+        <v/>
+      </c>
+      <c r="AH10" s="10">
+        <f>N10+S10+X10+AC10</f>
+        <v/>
+      </c>
+      <c r="AI10" s="10">
+        <f>O10+T10+Y10+AD10</f>
+        <v/>
+      </c>
+      <c r="AN10" s="8" t="n">
         <v>45943</v>
       </c>
-      <c r="AB10" s="8" t="n">
+      <c r="AO10" s="8" t="n">
         <v>45949</v>
       </c>
     </row>
@@ -1237,69 +1467,109 @@
         </is>
       </c>
       <c r="K11" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA11,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB11)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN11,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO11)</f>
         <v/>
       </c>
       <c r="L11" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA11,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB11)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN11,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO11)</f>
         <v/>
       </c>
       <c r="M11" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB11,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB11)</f>
+        <f>K11-L11</f>
         <v/>
       </c>
       <c r="N11" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA11,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB11)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN11,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO11)</f>
         <v/>
       </c>
       <c r="O11" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA11,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB11)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO11,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO11)</f>
         <v/>
       </c>
       <c r="P11" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB11,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB11)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN11,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO11)</f>
         <v/>
       </c>
       <c r="Q11" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA11,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB11)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN11,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO11)</f>
         <v/>
       </c>
       <c r="R11" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA11,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB11)</f>
+        <f>P11-Q11</f>
         <v/>
       </c>
       <c r="S11" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB11,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB11)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN11,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO11)</f>
         <v/>
       </c>
       <c r="T11" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA11,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB11)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO11,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO11)</f>
         <v/>
       </c>
       <c r="U11" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA11,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB11)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN11,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO11)</f>
         <v/>
       </c>
       <c r="V11" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB11,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB11)</f>
-        <v/>
-      </c>
-      <c r="W11" s="10">
-        <f>K11+N11+Q11+T11</f>
-        <v/>
-      </c>
-      <c r="X11" s="10">
-        <f>L11+O11+R11+U11</f>
-        <v/>
-      </c>
-      <c r="Y11" s="10">
-        <f>M11+P11+S11+V11</f>
-        <v/>
-      </c>
-      <c r="AA11" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN11,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO11)</f>
+        <v/>
+      </c>
+      <c r="W11" s="9">
+        <f>U11-V11</f>
+        <v/>
+      </c>
+      <c r="X11" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN11,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO11)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO11,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO11)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN11,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO11)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN11,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO11)</f>
+        <v/>
+      </c>
+      <c r="AB11" s="9">
+        <f>Z11-AA11</f>
+        <v/>
+      </c>
+      <c r="AC11" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN11,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO11)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO11,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO11)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="10">
+        <f>K11+P11+U11+Z11</f>
+        <v/>
+      </c>
+      <c r="AF11" s="10">
+        <f>L11+Q11+V11+AA11</f>
+        <v/>
+      </c>
+      <c r="AG11" s="10">
+        <f>M11+R11+W11+AB11</f>
+        <v/>
+      </c>
+      <c r="AH11" s="10">
+        <f>N11+S11+X11+AC11</f>
+        <v/>
+      </c>
+      <c r="AI11" s="10">
+        <f>O11+T11+Y11+AD11</f>
+        <v/>
+      </c>
+      <c r="AN11" s="8" t="n">
         <v>45950</v>
       </c>
-      <c r="AB11" s="8" t="n">
+      <c r="AO11" s="8" t="n">
         <v>45956</v>
       </c>
     </row>
@@ -1341,69 +1611,109 @@
         </is>
       </c>
       <c r="K12" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA12,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB12)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN12,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO12)</f>
         <v/>
       </c>
       <c r="L12" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA12,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB12)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN12,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO12)</f>
         <v/>
       </c>
       <c r="M12" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB12,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB12)</f>
+        <f>K12-L12</f>
         <v/>
       </c>
       <c r="N12" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA12,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB12)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN12,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO12)</f>
         <v/>
       </c>
       <c r="O12" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA12,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB12)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO12,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO12)</f>
         <v/>
       </c>
       <c r="P12" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB12,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB12)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN12,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO12)</f>
         <v/>
       </c>
       <c r="Q12" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA12,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB12)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN12,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO12)</f>
         <v/>
       </c>
       <c r="R12" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA12,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB12)</f>
+        <f>P12-Q12</f>
         <v/>
       </c>
       <c r="S12" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB12,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB12)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN12,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO12)</f>
         <v/>
       </c>
       <c r="T12" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA12,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB12)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO12,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO12)</f>
         <v/>
       </c>
       <c r="U12" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA12,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB12)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN12,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO12)</f>
         <v/>
       </c>
       <c r="V12" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB12,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB12)</f>
-        <v/>
-      </c>
-      <c r="W12" s="10">
-        <f>K12+N12+Q12+T12</f>
-        <v/>
-      </c>
-      <c r="X12" s="10">
-        <f>L12+O12+R12+U12</f>
-        <v/>
-      </c>
-      <c r="Y12" s="10">
-        <f>M12+P12+S12+V12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN12,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO12)</f>
+        <v/>
+      </c>
+      <c r="W12" s="9">
+        <f>U12-V12</f>
+        <v/>
+      </c>
+      <c r="X12" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN12,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO12)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO12,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO12)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN12,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO12)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN12,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO12)</f>
+        <v/>
+      </c>
+      <c r="AB12" s="9">
+        <f>Z12-AA12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN12,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO12)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO12,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO12)</f>
+        <v/>
+      </c>
+      <c r="AE12" s="10">
+        <f>K12+P12+U12+Z12</f>
+        <v/>
+      </c>
+      <c r="AF12" s="10">
+        <f>L12+Q12+V12+AA12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="10">
+        <f>M12+R12+W12+AB12</f>
+        <v/>
+      </c>
+      <c r="AH12" s="10">
+        <f>N12+S12+X12+AC12</f>
+        <v/>
+      </c>
+      <c r="AI12" s="10">
+        <f>O12+T12+Y12+AD12</f>
+        <v/>
+      </c>
+      <c r="AN12" s="8" t="n">
         <v>45957</v>
       </c>
-      <c r="AB12" s="8" t="n">
+      <c r="AO12" s="8" t="n">
         <v>45963</v>
       </c>
     </row>
@@ -1445,69 +1755,109 @@
         </is>
       </c>
       <c r="K13" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA13,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB13)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN13,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO13)</f>
         <v/>
       </c>
       <c r="L13" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA13,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB13)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN13,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO13)</f>
         <v/>
       </c>
       <c r="M13" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB13,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB13)</f>
+        <f>K13-L13</f>
         <v/>
       </c>
       <c r="N13" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA13,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB13)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN13,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO13)</f>
         <v/>
       </c>
       <c r="O13" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA13,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB13)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO13,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO13)</f>
         <v/>
       </c>
       <c r="P13" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB13,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB13)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN13,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO13)</f>
         <v/>
       </c>
       <c r="Q13" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA13,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB13)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN13,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO13)</f>
         <v/>
       </c>
       <c r="R13" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA13,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB13)</f>
+        <f>P13-Q13</f>
         <v/>
       </c>
       <c r="S13" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB13,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB13)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN13,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO13)</f>
         <v/>
       </c>
       <c r="T13" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA13,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB13)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO13,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO13)</f>
         <v/>
       </c>
       <c r="U13" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA13,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB13)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN13,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO13)</f>
         <v/>
       </c>
       <c r="V13" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB13,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB13)</f>
-        <v/>
-      </c>
-      <c r="W13" s="10">
-        <f>K13+N13+Q13+T13</f>
-        <v/>
-      </c>
-      <c r="X13" s="10">
-        <f>L13+O13+R13+U13</f>
-        <v/>
-      </c>
-      <c r="Y13" s="10">
-        <f>M13+P13+S13+V13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN13,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO13)</f>
+        <v/>
+      </c>
+      <c r="W13" s="9">
+        <f>U13-V13</f>
+        <v/>
+      </c>
+      <c r="X13" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN13,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO13)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO13,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO13)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN13,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO13)</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN13,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO13)</f>
+        <v/>
+      </c>
+      <c r="AB13" s="9">
+        <f>Z13-AA13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN13,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO13)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO13,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO13)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="10">
+        <f>K13+P13+U13+Z13</f>
+        <v/>
+      </c>
+      <c r="AF13" s="10">
+        <f>L13+Q13+V13+AA13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="10">
+        <f>M13+R13+W13+AB13</f>
+        <v/>
+      </c>
+      <c r="AH13" s="10">
+        <f>N13+S13+X13+AC13</f>
+        <v/>
+      </c>
+      <c r="AI13" s="10">
+        <f>O13+T13+Y13+AD13</f>
+        <v/>
+      </c>
+      <c r="AN13" s="8" t="n">
         <v>45964</v>
       </c>
-      <c r="AB13" s="8" t="n">
+      <c r="AO13" s="8" t="n">
         <v>45970</v>
       </c>
     </row>
@@ -1549,69 +1899,109 @@
         </is>
       </c>
       <c r="K14" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA14,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB14)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN14,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO14)</f>
         <v/>
       </c>
       <c r="L14" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA14,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB14)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN14,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO14)</f>
         <v/>
       </c>
       <c r="M14" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB14,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB14)</f>
+        <f>K14-L14</f>
         <v/>
       </c>
       <c r="N14" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA14,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB14)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN14,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO14)</f>
         <v/>
       </c>
       <c r="O14" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA14,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB14)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO14,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO14)</f>
         <v/>
       </c>
       <c r="P14" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB14,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB14)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN14,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO14)</f>
         <v/>
       </c>
       <c r="Q14" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA14,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB14)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN14,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO14)</f>
         <v/>
       </c>
       <c r="R14" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA14,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB14)</f>
+        <f>P14-Q14</f>
         <v/>
       </c>
       <c r="S14" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB14,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB14)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN14,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO14)</f>
         <v/>
       </c>
       <c r="T14" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA14,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB14)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO14,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO14)</f>
         <v/>
       </c>
       <c r="U14" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA14,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB14)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN14,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO14)</f>
         <v/>
       </c>
       <c r="V14" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB14,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB14)</f>
-        <v/>
-      </c>
-      <c r="W14" s="10">
-        <f>K14+N14+Q14+T14</f>
-        <v/>
-      </c>
-      <c r="X14" s="10">
-        <f>L14+O14+R14+U14</f>
-        <v/>
-      </c>
-      <c r="Y14" s="10">
-        <f>M14+P14+S14+V14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN14,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO14)</f>
+        <v/>
+      </c>
+      <c r="W14" s="9">
+        <f>U14-V14</f>
+        <v/>
+      </c>
+      <c r="X14" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN14,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO14)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO14,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO14)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN14,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO14)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN14,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO14)</f>
+        <v/>
+      </c>
+      <c r="AB14" s="9">
+        <f>Z14-AA14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN14,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO14)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO14,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO14)</f>
+        <v/>
+      </c>
+      <c r="AE14" s="10">
+        <f>K14+P14+U14+Z14</f>
+        <v/>
+      </c>
+      <c r="AF14" s="10">
+        <f>L14+Q14+V14+AA14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="10">
+        <f>M14+R14+W14+AB14</f>
+        <v/>
+      </c>
+      <c r="AH14" s="10">
+        <f>N14+S14+X14+AC14</f>
+        <v/>
+      </c>
+      <c r="AI14" s="10">
+        <f>O14+T14+Y14+AD14</f>
+        <v/>
+      </c>
+      <c r="AN14" s="8" t="n">
         <v>45971</v>
       </c>
-      <c r="AB14" s="8" t="n">
+      <c r="AO14" s="8" t="n">
         <v>45977</v>
       </c>
     </row>
@@ -1653,69 +2043,109 @@
         </is>
       </c>
       <c r="K15" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA15,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB15)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN15,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO15)</f>
         <v/>
       </c>
       <c r="L15" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA15,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB15)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN15,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO15)</f>
         <v/>
       </c>
       <c r="M15" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB15,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB15)</f>
+        <f>K15-L15</f>
         <v/>
       </c>
       <c r="N15" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA15,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB15)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN15,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO15)</f>
         <v/>
       </c>
       <c r="O15" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA15,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB15)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO15,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO15)</f>
         <v/>
       </c>
       <c r="P15" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB15,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB15)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN15,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO15)</f>
         <v/>
       </c>
       <c r="Q15" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA15,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB15)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN15,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO15)</f>
         <v/>
       </c>
       <c r="R15" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA15,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB15)</f>
+        <f>P15-Q15</f>
         <v/>
       </c>
       <c r="S15" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB15,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB15)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN15,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO15)</f>
         <v/>
       </c>
       <c r="T15" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA15,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB15)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO15,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO15)</f>
         <v/>
       </c>
       <c r="U15" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA15,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB15)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN15,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO15)</f>
         <v/>
       </c>
       <c r="V15" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB15,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB15)</f>
-        <v/>
-      </c>
-      <c r="W15" s="10">
-        <f>K15+N15+Q15+T15</f>
-        <v/>
-      </c>
-      <c r="X15" s="10">
-        <f>L15+O15+R15+U15</f>
-        <v/>
-      </c>
-      <c r="Y15" s="10">
-        <f>M15+P15+S15+V15</f>
-        <v/>
-      </c>
-      <c r="AA15" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN15,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO15)</f>
+        <v/>
+      </c>
+      <c r="W15" s="9">
+        <f>U15-V15</f>
+        <v/>
+      </c>
+      <c r="X15" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN15,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO15)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO15,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO15)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN15,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO15)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN15,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO15)</f>
+        <v/>
+      </c>
+      <c r="AB15" s="9">
+        <f>Z15-AA15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN15,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO15)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO15,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO15)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="10">
+        <f>K15+P15+U15+Z15</f>
+        <v/>
+      </c>
+      <c r="AF15" s="10">
+        <f>L15+Q15+V15+AA15</f>
+        <v/>
+      </c>
+      <c r="AG15" s="10">
+        <f>M15+R15+W15+AB15</f>
+        <v/>
+      </c>
+      <c r="AH15" s="10">
+        <f>N15+S15+X15+AC15</f>
+        <v/>
+      </c>
+      <c r="AI15" s="10">
+        <f>O15+T15+Y15+AD15</f>
+        <v/>
+      </c>
+      <c r="AN15" s="8" t="n">
         <v>45978</v>
       </c>
-      <c r="AB15" s="8" t="n">
+      <c r="AO15" s="8" t="n">
         <v>45984</v>
       </c>
     </row>
@@ -1757,69 +2187,109 @@
         </is>
       </c>
       <c r="K16" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA16,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB16)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN16,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO16)</f>
         <v/>
       </c>
       <c r="L16" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA16,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB16)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN16,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO16)</f>
         <v/>
       </c>
       <c r="M16" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB16,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB16)</f>
+        <f>K16-L16</f>
         <v/>
       </c>
       <c r="N16" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA16,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB16)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN16,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO16)</f>
         <v/>
       </c>
       <c r="O16" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA16,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB16)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO16,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO16)</f>
         <v/>
       </c>
       <c r="P16" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB16,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB16)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN16,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO16)</f>
         <v/>
       </c>
       <c r="Q16" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA16,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB16)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN16,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO16)</f>
         <v/>
       </c>
       <c r="R16" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA16,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB16)</f>
+        <f>P16-Q16</f>
         <v/>
       </c>
       <c r="S16" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB16,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB16)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN16,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO16)</f>
         <v/>
       </c>
       <c r="T16" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA16,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB16)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO16,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO16)</f>
         <v/>
       </c>
       <c r="U16" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA16,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB16)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN16,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO16)</f>
         <v/>
       </c>
       <c r="V16" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB16,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB16)</f>
-        <v/>
-      </c>
-      <c r="W16" s="10">
-        <f>K16+N16+Q16+T16</f>
-        <v/>
-      </c>
-      <c r="X16" s="10">
-        <f>L16+O16+R16+U16</f>
-        <v/>
-      </c>
-      <c r="Y16" s="10">
-        <f>M16+P16+S16+V16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN16,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO16)</f>
+        <v/>
+      </c>
+      <c r="W16" s="9">
+        <f>U16-V16</f>
+        <v/>
+      </c>
+      <c r="X16" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN16,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO16)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO16,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO16)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN16,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO16)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN16,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO16)</f>
+        <v/>
+      </c>
+      <c r="AB16" s="9">
+        <f>Z16-AA16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN16,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO16)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO16,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO16)</f>
+        <v/>
+      </c>
+      <c r="AE16" s="10">
+        <f>K16+P16+U16+Z16</f>
+        <v/>
+      </c>
+      <c r="AF16" s="10">
+        <f>L16+Q16+V16+AA16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="10">
+        <f>M16+R16+W16+AB16</f>
+        <v/>
+      </c>
+      <c r="AH16" s="10">
+        <f>N16+S16+X16+AC16</f>
+        <v/>
+      </c>
+      <c r="AI16" s="10">
+        <f>O16+T16+Y16+AD16</f>
+        <v/>
+      </c>
+      <c r="AN16" s="8" t="n">
         <v>45985</v>
       </c>
-      <c r="AB16" s="8" t="n">
+      <c r="AO16" s="8" t="n">
         <v>45991</v>
       </c>
     </row>
@@ -1861,69 +2331,109 @@
         </is>
       </c>
       <c r="K17" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA17,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB17)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN17,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO17)</f>
         <v/>
       </c>
       <c r="L17" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA17,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB17)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN17,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO17)</f>
         <v/>
       </c>
       <c r="M17" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB17,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB17)</f>
+        <f>K17-L17</f>
         <v/>
       </c>
       <c r="N17" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA17,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB17)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN17,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO17)</f>
         <v/>
       </c>
       <c r="O17" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA17,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB17)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO17,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO17)</f>
         <v/>
       </c>
       <c r="P17" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB17,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB17)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN17,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO17)</f>
         <v/>
       </c>
       <c r="Q17" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA17,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB17)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN17,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO17)</f>
         <v/>
       </c>
       <c r="R17" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA17,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB17)</f>
+        <f>P17-Q17</f>
         <v/>
       </c>
       <c r="S17" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB17,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB17)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN17,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO17)</f>
         <v/>
       </c>
       <c r="T17" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA17,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB17)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO17,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO17)</f>
         <v/>
       </c>
       <c r="U17" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA17,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB17)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN17,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO17)</f>
         <v/>
       </c>
       <c r="V17" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB17,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB17)</f>
-        <v/>
-      </c>
-      <c r="W17" s="10">
-        <f>K17+N17+Q17+T17</f>
-        <v/>
-      </c>
-      <c r="X17" s="10">
-        <f>L17+O17+R17+U17</f>
-        <v/>
-      </c>
-      <c r="Y17" s="10">
-        <f>M17+P17+S17+V17</f>
-        <v/>
-      </c>
-      <c r="AA17" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN17,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO17)</f>
+        <v/>
+      </c>
+      <c r="W17" s="9">
+        <f>U17-V17</f>
+        <v/>
+      </c>
+      <c r="X17" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN17,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO17)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO17,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO17)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN17,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO17)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN17,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO17)</f>
+        <v/>
+      </c>
+      <c r="AB17" s="9">
+        <f>Z17-AA17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN17,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO17)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO17,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO17)</f>
+        <v/>
+      </c>
+      <c r="AE17" s="10">
+        <f>K17+P17+U17+Z17</f>
+        <v/>
+      </c>
+      <c r="AF17" s="10">
+        <f>L17+Q17+V17+AA17</f>
+        <v/>
+      </c>
+      <c r="AG17" s="10">
+        <f>M17+R17+W17+AB17</f>
+        <v/>
+      </c>
+      <c r="AH17" s="10">
+        <f>N17+S17+X17+AC17</f>
+        <v/>
+      </c>
+      <c r="AI17" s="10">
+        <f>O17+T17+Y17+AD17</f>
+        <v/>
+      </c>
+      <c r="AN17" s="8" t="n">
         <v>45992</v>
       </c>
-      <c r="AB17" s="8" t="n">
+      <c r="AO17" s="8" t="n">
         <v>45998</v>
       </c>
     </row>
@@ -1965,69 +2475,109 @@
         </is>
       </c>
       <c r="K18" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA18,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB18)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN18,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO18)</f>
         <v/>
       </c>
       <c r="L18" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA18,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB18)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN18,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO18)</f>
         <v/>
       </c>
       <c r="M18" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB18,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB18)</f>
+        <f>K18-L18</f>
         <v/>
       </c>
       <c r="N18" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA18,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB18)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN18,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO18)</f>
         <v/>
       </c>
       <c r="O18" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA18,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB18)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO18,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO18)</f>
         <v/>
       </c>
       <c r="P18" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB18,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB18)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN18,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO18)</f>
         <v/>
       </c>
       <c r="Q18" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA18,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB18)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN18,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO18)</f>
         <v/>
       </c>
       <c r="R18" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA18,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB18)</f>
+        <f>P18-Q18</f>
         <v/>
       </c>
       <c r="S18" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB18,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB18)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN18,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO18)</f>
         <v/>
       </c>
       <c r="T18" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA18,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB18)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO18,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO18)</f>
         <v/>
       </c>
       <c r="U18" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA18,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB18)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN18,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO18)</f>
         <v/>
       </c>
       <c r="V18" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB18,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB18)</f>
-        <v/>
-      </c>
-      <c r="W18" s="10">
-        <f>K18+N18+Q18+T18</f>
-        <v/>
-      </c>
-      <c r="X18" s="10">
-        <f>L18+O18+R18+U18</f>
-        <v/>
-      </c>
-      <c r="Y18" s="10">
-        <f>M18+P18+S18+V18</f>
-        <v/>
-      </c>
-      <c r="AA18" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN18,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO18)</f>
+        <v/>
+      </c>
+      <c r="W18" s="9">
+        <f>U18-V18</f>
+        <v/>
+      </c>
+      <c r="X18" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN18,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO18)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO18,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO18)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN18,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO18)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN18,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO18)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="9">
+        <f>Z18-AA18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN18,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO18)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO18,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO18)</f>
+        <v/>
+      </c>
+      <c r="AE18" s="10">
+        <f>K18+P18+U18+Z18</f>
+        <v/>
+      </c>
+      <c r="AF18" s="10">
+        <f>L18+Q18+V18+AA18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="10">
+        <f>M18+R18+W18+AB18</f>
+        <v/>
+      </c>
+      <c r="AH18" s="10">
+        <f>N18+S18+X18+AC18</f>
+        <v/>
+      </c>
+      <c r="AI18" s="10">
+        <f>O18+T18+Y18+AD18</f>
+        <v/>
+      </c>
+      <c r="AN18" s="8" t="n">
         <v>45999</v>
       </c>
-      <c r="AB18" s="8" t="n">
+      <c r="AO18" s="8" t="n">
         <v>46005</v>
       </c>
     </row>
@@ -2069,69 +2619,109 @@
         </is>
       </c>
       <c r="K19" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA19,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB19)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN19,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO19)</f>
         <v/>
       </c>
       <c r="L19" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA19,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB19)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN19,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO19)</f>
         <v/>
       </c>
       <c r="M19" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB19,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB19)</f>
+        <f>K19-L19</f>
         <v/>
       </c>
       <c r="N19" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA19,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB19)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN19,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO19)</f>
         <v/>
       </c>
       <c r="O19" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA19,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB19)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO19,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO19)</f>
         <v/>
       </c>
       <c r="P19" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB19,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB19)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN19,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO19)</f>
         <v/>
       </c>
       <c r="Q19" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA19,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB19)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN19,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO19)</f>
         <v/>
       </c>
       <c r="R19" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA19,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB19)</f>
+        <f>P19-Q19</f>
         <v/>
       </c>
       <c r="S19" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB19,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB19)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN19,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO19)</f>
         <v/>
       </c>
       <c r="T19" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA19,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB19)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO19,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO19)</f>
         <v/>
       </c>
       <c r="U19" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA19,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB19)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN19,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO19)</f>
         <v/>
       </c>
       <c r="V19" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB19,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB19)</f>
-        <v/>
-      </c>
-      <c r="W19" s="10">
-        <f>K19+N19+Q19+T19</f>
-        <v/>
-      </c>
-      <c r="X19" s="10">
-        <f>L19+O19+R19+U19</f>
-        <v/>
-      </c>
-      <c r="Y19" s="10">
-        <f>M19+P19+S19+V19</f>
-        <v/>
-      </c>
-      <c r="AA19" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN19,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO19)</f>
+        <v/>
+      </c>
+      <c r="W19" s="9">
+        <f>U19-V19</f>
+        <v/>
+      </c>
+      <c r="X19" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN19,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO19)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO19,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO19)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN19,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO19)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN19,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO19)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="9">
+        <f>Z19-AA19</f>
+        <v/>
+      </c>
+      <c r="AC19" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN19,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO19)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO19,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO19)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="10">
+        <f>K19+P19+U19+Z19</f>
+        <v/>
+      </c>
+      <c r="AF19" s="10">
+        <f>L19+Q19+V19+AA19</f>
+        <v/>
+      </c>
+      <c r="AG19" s="10">
+        <f>M19+R19+W19+AB19</f>
+        <v/>
+      </c>
+      <c r="AH19" s="10">
+        <f>N19+S19+X19+AC19</f>
+        <v/>
+      </c>
+      <c r="AI19" s="10">
+        <f>O19+T19+Y19+AD19</f>
+        <v/>
+      </c>
+      <c r="AN19" s="8" t="n">
         <v>46006</v>
       </c>
-      <c r="AB19" s="8" t="n">
+      <c r="AO19" s="8" t="n">
         <v>46012</v>
       </c>
     </row>
@@ -2173,69 +2763,109 @@
         </is>
       </c>
       <c r="K20" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA20,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB20)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN20,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO20)</f>
         <v/>
       </c>
       <c r="L20" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA20,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB20)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN20,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO20)</f>
         <v/>
       </c>
       <c r="M20" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB20,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB20)</f>
+        <f>K20-L20</f>
         <v/>
       </c>
       <c r="N20" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA20,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB20)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN20,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO20)</f>
         <v/>
       </c>
       <c r="O20" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA20,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB20)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO20,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO20)</f>
         <v/>
       </c>
       <c r="P20" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB20,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB20)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN20,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO20)</f>
         <v/>
       </c>
       <c r="Q20" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA20,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB20)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN20,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO20)</f>
         <v/>
       </c>
       <c r="R20" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA20,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB20)</f>
+        <f>P20-Q20</f>
         <v/>
       </c>
       <c r="S20" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB20,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB20)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN20,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO20)</f>
         <v/>
       </c>
       <c r="T20" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA20,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB20)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO20,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO20)</f>
         <v/>
       </c>
       <c r="U20" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA20,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB20)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN20,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO20)</f>
         <v/>
       </c>
       <c r="V20" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB20,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB20)</f>
-        <v/>
-      </c>
-      <c r="W20" s="10">
-        <f>K20+N20+Q20+T20</f>
-        <v/>
-      </c>
-      <c r="X20" s="10">
-        <f>L20+O20+R20+U20</f>
-        <v/>
-      </c>
-      <c r="Y20" s="10">
-        <f>M20+P20+S20+V20</f>
-        <v/>
-      </c>
-      <c r="AA20" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN20,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO20)</f>
+        <v/>
+      </c>
+      <c r="W20" s="9">
+        <f>U20-V20</f>
+        <v/>
+      </c>
+      <c r="X20" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN20,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO20)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO20,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO20)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN20,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO20)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN20,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO20)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="9">
+        <f>Z20-AA20</f>
+        <v/>
+      </c>
+      <c r="AC20" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN20,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO20)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO20,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO20)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="10">
+        <f>K20+P20+U20+Z20</f>
+        <v/>
+      </c>
+      <c r="AF20" s="10">
+        <f>L20+Q20+V20+AA20</f>
+        <v/>
+      </c>
+      <c r="AG20" s="10">
+        <f>M20+R20+W20+AB20</f>
+        <v/>
+      </c>
+      <c r="AH20" s="10">
+        <f>N20+S20+X20+AC20</f>
+        <v/>
+      </c>
+      <c r="AI20" s="10">
+        <f>O20+T20+Y20+AD20</f>
+        <v/>
+      </c>
+      <c r="AN20" s="8" t="n">
         <v>46013</v>
       </c>
-      <c r="AB20" s="8" t="n">
+      <c r="AO20" s="8" t="n">
         <v>46019</v>
       </c>
     </row>
@@ -2277,69 +2907,109 @@
         </is>
       </c>
       <c r="K21" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA21,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB21)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN21,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO21)</f>
         <v/>
       </c>
       <c r="L21" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA21,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB21)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN21,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO21)</f>
         <v/>
       </c>
       <c r="M21" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB21,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB21)</f>
+        <f>K21-L21</f>
         <v/>
       </c>
       <c r="N21" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA21,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB21)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN21,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO21)</f>
         <v/>
       </c>
       <c r="O21" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA21,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB21)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO21,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO21)</f>
         <v/>
       </c>
       <c r="P21" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB21,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB21)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN21,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO21)</f>
         <v/>
       </c>
       <c r="Q21" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA21,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB21)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN21,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO21)</f>
         <v/>
       </c>
       <c r="R21" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA21,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB21)</f>
+        <f>P21-Q21</f>
         <v/>
       </c>
       <c r="S21" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB21,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB21)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN21,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO21)</f>
         <v/>
       </c>
       <c r="T21" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA21,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB21)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO21,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO21)</f>
         <v/>
       </c>
       <c r="U21" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA21,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB21)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN21,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO21)</f>
         <v/>
       </c>
       <c r="V21" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB21,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB21)</f>
-        <v/>
-      </c>
-      <c r="W21" s="10">
-        <f>K21+N21+Q21+T21</f>
-        <v/>
-      </c>
-      <c r="X21" s="10">
-        <f>L21+O21+R21+U21</f>
-        <v/>
-      </c>
-      <c r="Y21" s="10">
-        <f>M21+P21+S21+V21</f>
-        <v/>
-      </c>
-      <c r="AA21" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN21,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO21)</f>
+        <v/>
+      </c>
+      <c r="W21" s="9">
+        <f>U21-V21</f>
+        <v/>
+      </c>
+      <c r="X21" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN21,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO21)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO21,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO21)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN21,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO21)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN21,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO21)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="9">
+        <f>Z21-AA21</f>
+        <v/>
+      </c>
+      <c r="AC21" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN21,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO21)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO21,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO21)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="10">
+        <f>K21+P21+U21+Z21</f>
+        <v/>
+      </c>
+      <c r="AF21" s="10">
+        <f>L21+Q21+V21+AA21</f>
+        <v/>
+      </c>
+      <c r="AG21" s="10">
+        <f>M21+R21+W21+AB21</f>
+        <v/>
+      </c>
+      <c r="AH21" s="10">
+        <f>N21+S21+X21+AC21</f>
+        <v/>
+      </c>
+      <c r="AI21" s="10">
+        <f>O21+T21+Y21+AD21</f>
+        <v/>
+      </c>
+      <c r="AN21" s="8" t="n">
         <v>46020</v>
       </c>
-      <c r="AB21" s="8" t="n">
+      <c r="AO21" s="8" t="n">
         <v>46026</v>
       </c>
     </row>
@@ -2381,69 +3051,109 @@
         </is>
       </c>
       <c r="K22" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA22,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB22)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN22,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO22)</f>
         <v/>
       </c>
       <c r="L22" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA22,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB22)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN22,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO22)</f>
         <v/>
       </c>
       <c r="M22" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB22,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB22)</f>
+        <f>K22-L22</f>
         <v/>
       </c>
       <c r="N22" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA22,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB22)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN22,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO22)</f>
         <v/>
       </c>
       <c r="O22" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA22,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB22)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO22,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO22)</f>
         <v/>
       </c>
       <c r="P22" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB22,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB22)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN22,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO22)</f>
         <v/>
       </c>
       <c r="Q22" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA22,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB22)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN22,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO22)</f>
         <v/>
       </c>
       <c r="R22" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA22,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB22)</f>
+        <f>P22-Q22</f>
         <v/>
       </c>
       <c r="S22" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB22,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB22)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN22,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO22)</f>
         <v/>
       </c>
       <c r="T22" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA22,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB22)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO22,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO22)</f>
         <v/>
       </c>
       <c r="U22" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA22,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB22)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN22,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO22)</f>
         <v/>
       </c>
       <c r="V22" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB22,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB22)</f>
-        <v/>
-      </c>
-      <c r="W22" s="10">
-        <f>K22+N22+Q22+T22</f>
-        <v/>
-      </c>
-      <c r="X22" s="10">
-        <f>L22+O22+R22+U22</f>
-        <v/>
-      </c>
-      <c r="Y22" s="10">
-        <f>M22+P22+S22+V22</f>
-        <v/>
-      </c>
-      <c r="AA22" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN22,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO22)</f>
+        <v/>
+      </c>
+      <c r="W22" s="9">
+        <f>U22-V22</f>
+        <v/>
+      </c>
+      <c r="X22" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN22,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO22)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO22,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO22)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN22,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO22)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN22,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO22)</f>
+        <v/>
+      </c>
+      <c r="AB22" s="9">
+        <f>Z22-AA22</f>
+        <v/>
+      </c>
+      <c r="AC22" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN22,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO22)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO22,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO22)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="10">
+        <f>K22+P22+U22+Z22</f>
+        <v/>
+      </c>
+      <c r="AF22" s="10">
+        <f>L22+Q22+V22+AA22</f>
+        <v/>
+      </c>
+      <c r="AG22" s="10">
+        <f>M22+R22+W22+AB22</f>
+        <v/>
+      </c>
+      <c r="AH22" s="10">
+        <f>N22+S22+X22+AC22</f>
+        <v/>
+      </c>
+      <c r="AI22" s="10">
+        <f>O22+T22+Y22+AD22</f>
+        <v/>
+      </c>
+      <c r="AN22" s="8" t="n">
         <v>46027</v>
       </c>
-      <c r="AB22" s="8" t="n">
+      <c r="AO22" s="8" t="n">
         <v>46033</v>
       </c>
     </row>
@@ -2485,69 +3195,109 @@
         </is>
       </c>
       <c r="K23" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA23,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB23)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN23,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO23)</f>
         <v/>
       </c>
       <c r="L23" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA23,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB23)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN23,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO23)</f>
         <v/>
       </c>
       <c r="M23" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB23,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB23)</f>
+        <f>K23-L23</f>
         <v/>
       </c>
       <c r="N23" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA23,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB23)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN23,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO23)</f>
         <v/>
       </c>
       <c r="O23" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA23,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB23)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO23,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO23)</f>
         <v/>
       </c>
       <c r="P23" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB23,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB23)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN23,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO23)</f>
         <v/>
       </c>
       <c r="Q23" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA23,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB23)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN23,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO23)</f>
         <v/>
       </c>
       <c r="R23" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA23,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB23)</f>
+        <f>P23-Q23</f>
         <v/>
       </c>
       <c r="S23" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB23,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB23)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN23,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO23)</f>
         <v/>
       </c>
       <c r="T23" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA23,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB23)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO23,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO23)</f>
         <v/>
       </c>
       <c r="U23" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA23,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB23)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN23,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO23)</f>
         <v/>
       </c>
       <c r="V23" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB23,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB23)</f>
-        <v/>
-      </c>
-      <c r="W23" s="10">
-        <f>K23+N23+Q23+T23</f>
-        <v/>
-      </c>
-      <c r="X23" s="10">
-        <f>L23+O23+R23+U23</f>
-        <v/>
-      </c>
-      <c r="Y23" s="10">
-        <f>M23+P23+S23+V23</f>
-        <v/>
-      </c>
-      <c r="AA23" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN23,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO23)</f>
+        <v/>
+      </c>
+      <c r="W23" s="9">
+        <f>U23-V23</f>
+        <v/>
+      </c>
+      <c r="X23" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN23,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO23)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO23,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO23)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN23,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO23)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN23,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO23)</f>
+        <v/>
+      </c>
+      <c r="AB23" s="9">
+        <f>Z23-AA23</f>
+        <v/>
+      </c>
+      <c r="AC23" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN23,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO23)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO23,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO23)</f>
+        <v/>
+      </c>
+      <c r="AE23" s="10">
+        <f>K23+P23+U23+Z23</f>
+        <v/>
+      </c>
+      <c r="AF23" s="10">
+        <f>L23+Q23+V23+AA23</f>
+        <v/>
+      </c>
+      <c r="AG23" s="10">
+        <f>M23+R23+W23+AB23</f>
+        <v/>
+      </c>
+      <c r="AH23" s="10">
+        <f>N23+S23+X23+AC23</f>
+        <v/>
+      </c>
+      <c r="AI23" s="10">
+        <f>O23+T23+Y23+AD23</f>
+        <v/>
+      </c>
+      <c r="AN23" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="AB23" s="8" t="n">
+      <c r="AO23" s="8" t="n">
         <v>46040</v>
       </c>
     </row>
@@ -2589,69 +3339,109 @@
         </is>
       </c>
       <c r="K24" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA24,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB24)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN24,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO24)</f>
         <v/>
       </c>
       <c r="L24" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA24,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB24)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN24,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO24)</f>
         <v/>
       </c>
       <c r="M24" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB24,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB24)</f>
+        <f>K24-L24</f>
         <v/>
       </c>
       <c r="N24" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA24,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB24)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN24,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO24)</f>
         <v/>
       </c>
       <c r="O24" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA24,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB24)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO24,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO24)</f>
         <v/>
       </c>
       <c r="P24" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB24,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB24)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN24,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO24)</f>
         <v/>
       </c>
       <c r="Q24" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA24,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB24)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN24,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO24)</f>
         <v/>
       </c>
       <c r="R24" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA24,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB24)</f>
+        <f>P24-Q24</f>
         <v/>
       </c>
       <c r="S24" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB24,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB24)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN24,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO24)</f>
         <v/>
       </c>
       <c r="T24" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA24,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB24)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO24,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO24)</f>
         <v/>
       </c>
       <c r="U24" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA24,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB24)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN24,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO24)</f>
         <v/>
       </c>
       <c r="V24" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB24,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB24)</f>
-        <v/>
-      </c>
-      <c r="W24" s="10">
-        <f>K24+N24+Q24+T24</f>
-        <v/>
-      </c>
-      <c r="X24" s="10">
-        <f>L24+O24+R24+U24</f>
-        <v/>
-      </c>
-      <c r="Y24" s="10">
-        <f>M24+P24+S24+V24</f>
-        <v/>
-      </c>
-      <c r="AA24" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN24,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO24)</f>
+        <v/>
+      </c>
+      <c r="W24" s="9">
+        <f>U24-V24</f>
+        <v/>
+      </c>
+      <c r="X24" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN24,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO24)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO24,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO24)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN24,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO24)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN24,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO24)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="9">
+        <f>Z24-AA24</f>
+        <v/>
+      </c>
+      <c r="AC24" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN24,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO24)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO24,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO24)</f>
+        <v/>
+      </c>
+      <c r="AE24" s="10">
+        <f>K24+P24+U24+Z24</f>
+        <v/>
+      </c>
+      <c r="AF24" s="10">
+        <f>L24+Q24+V24+AA24</f>
+        <v/>
+      </c>
+      <c r="AG24" s="10">
+        <f>M24+R24+W24+AB24</f>
+        <v/>
+      </c>
+      <c r="AH24" s="10">
+        <f>N24+S24+X24+AC24</f>
+        <v/>
+      </c>
+      <c r="AI24" s="10">
+        <f>O24+T24+Y24+AD24</f>
+        <v/>
+      </c>
+      <c r="AN24" s="8" t="n">
         <v>46041</v>
       </c>
-      <c r="AB24" s="8" t="n">
+      <c r="AO24" s="8" t="n">
         <v>46047</v>
       </c>
     </row>
@@ -2693,69 +3483,109 @@
         </is>
       </c>
       <c r="K25" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA25,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB25)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN25,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO25)</f>
         <v/>
       </c>
       <c r="L25" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA25,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB25)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN25,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO25)</f>
         <v/>
       </c>
       <c r="M25" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB25,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB25)</f>
+        <f>K25-L25</f>
         <v/>
       </c>
       <c r="N25" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA25,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB25)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN25,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO25)</f>
         <v/>
       </c>
       <c r="O25" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA25,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB25)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO25,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO25)</f>
         <v/>
       </c>
       <c r="P25" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB25,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB25)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN25,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO25)</f>
         <v/>
       </c>
       <c r="Q25" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA25,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB25)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN25,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO25)</f>
         <v/>
       </c>
       <c r="R25" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA25,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB25)</f>
+        <f>P25-Q25</f>
         <v/>
       </c>
       <c r="S25" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB25,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB25)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN25,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO25)</f>
         <v/>
       </c>
       <c r="T25" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA25,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB25)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO25,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO25)</f>
         <v/>
       </c>
       <c r="U25" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA25,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB25)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN25,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO25)</f>
         <v/>
       </c>
       <c r="V25" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB25,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB25)</f>
-        <v/>
-      </c>
-      <c r="W25" s="10">
-        <f>K25+N25+Q25+T25</f>
-        <v/>
-      </c>
-      <c r="X25" s="10">
-        <f>L25+O25+R25+U25</f>
-        <v/>
-      </c>
-      <c r="Y25" s="10">
-        <f>M25+P25+S25+V25</f>
-        <v/>
-      </c>
-      <c r="AA25" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN25,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO25)</f>
+        <v/>
+      </c>
+      <c r="W25" s="9">
+        <f>U25-V25</f>
+        <v/>
+      </c>
+      <c r="X25" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN25,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO25)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO25,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO25)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN25,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO25)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN25,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO25)</f>
+        <v/>
+      </c>
+      <c r="AB25" s="9">
+        <f>Z25-AA25</f>
+        <v/>
+      </c>
+      <c r="AC25" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN25,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO25)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO25,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO25)</f>
+        <v/>
+      </c>
+      <c r="AE25" s="10">
+        <f>K25+P25+U25+Z25</f>
+        <v/>
+      </c>
+      <c r="AF25" s="10">
+        <f>L25+Q25+V25+AA25</f>
+        <v/>
+      </c>
+      <c r="AG25" s="10">
+        <f>M25+R25+W25+AB25</f>
+        <v/>
+      </c>
+      <c r="AH25" s="10">
+        <f>N25+S25+X25+AC25</f>
+        <v/>
+      </c>
+      <c r="AI25" s="10">
+        <f>O25+T25+Y25+AD25</f>
+        <v/>
+      </c>
+      <c r="AN25" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="AB25" s="8" t="n">
+      <c r="AO25" s="8" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -2797,69 +3627,109 @@
         </is>
       </c>
       <c r="K26" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA26,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB26)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN26,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO26)</f>
         <v/>
       </c>
       <c r="L26" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA26,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB26)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN26,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO26)</f>
         <v/>
       </c>
       <c r="M26" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB26,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB26)</f>
+        <f>K26-L26</f>
         <v/>
       </c>
       <c r="N26" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA26,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB26)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN26,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO26)</f>
         <v/>
       </c>
       <c r="O26" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA26,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB26)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO26,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO26)</f>
         <v/>
       </c>
       <c r="P26" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB26,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB26)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN26,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO26)</f>
         <v/>
       </c>
       <c r="Q26" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA26,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB26)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN26,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO26)</f>
         <v/>
       </c>
       <c r="R26" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA26,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB26)</f>
+        <f>P26-Q26</f>
         <v/>
       </c>
       <c r="S26" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB26,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB26)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN26,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO26)</f>
         <v/>
       </c>
       <c r="T26" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA26,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB26)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO26,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO26)</f>
         <v/>
       </c>
       <c r="U26" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA26,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB26)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN26,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO26)</f>
         <v/>
       </c>
       <c r="V26" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB26,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB26)</f>
-        <v/>
-      </c>
-      <c r="W26" s="10">
-        <f>K26+N26+Q26+T26</f>
-        <v/>
-      </c>
-      <c r="X26" s="10">
-        <f>L26+O26+R26+U26</f>
-        <v/>
-      </c>
-      <c r="Y26" s="10">
-        <f>M26+P26+S26+V26</f>
-        <v/>
-      </c>
-      <c r="AA26" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN26,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO26)</f>
+        <v/>
+      </c>
+      <c r="W26" s="9">
+        <f>U26-V26</f>
+        <v/>
+      </c>
+      <c r="X26" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN26,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO26)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO26,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO26)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN26,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO26)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN26,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO26)</f>
+        <v/>
+      </c>
+      <c r="AB26" s="9">
+        <f>Z26-AA26</f>
+        <v/>
+      </c>
+      <c r="AC26" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN26,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO26)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO26,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO26)</f>
+        <v/>
+      </c>
+      <c r="AE26" s="10">
+        <f>K26+P26+U26+Z26</f>
+        <v/>
+      </c>
+      <c r="AF26" s="10">
+        <f>L26+Q26+V26+AA26</f>
+        <v/>
+      </c>
+      <c r="AG26" s="10">
+        <f>M26+R26+W26+AB26</f>
+        <v/>
+      </c>
+      <c r="AH26" s="10">
+        <f>N26+S26+X26+AC26</f>
+        <v/>
+      </c>
+      <c r="AI26" s="10">
+        <f>O26+T26+Y26+AD26</f>
+        <v/>
+      </c>
+      <c r="AN26" s="8" t="n">
         <v>46055</v>
       </c>
-      <c r="AB26" s="8" t="n">
+      <c r="AO26" s="8" t="n">
         <v>46061</v>
       </c>
     </row>
@@ -2901,69 +3771,109 @@
         </is>
       </c>
       <c r="K27" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA27,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB27)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN27,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO27)</f>
         <v/>
       </c>
       <c r="L27" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA27,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB27)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN27,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO27)</f>
         <v/>
       </c>
       <c r="M27" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB27,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB27)</f>
+        <f>K27-L27</f>
         <v/>
       </c>
       <c r="N27" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA27,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB27)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN27,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO27)</f>
         <v/>
       </c>
       <c r="O27" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA27,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB27)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO27,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO27)</f>
         <v/>
       </c>
       <c r="P27" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB27,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB27)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN27,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO27)</f>
         <v/>
       </c>
       <c r="Q27" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA27,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB27)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN27,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO27)</f>
         <v/>
       </c>
       <c r="R27" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA27,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB27)</f>
+        <f>P27-Q27</f>
         <v/>
       </c>
       <c r="S27" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB27,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB27)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN27,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO27)</f>
         <v/>
       </c>
       <c r="T27" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA27,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB27)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO27,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO27)</f>
         <v/>
       </c>
       <c r="U27" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA27,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB27)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN27,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO27)</f>
         <v/>
       </c>
       <c r="V27" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB27,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB27)</f>
-        <v/>
-      </c>
-      <c r="W27" s="10">
-        <f>K27+N27+Q27+T27</f>
-        <v/>
-      </c>
-      <c r="X27" s="10">
-        <f>L27+O27+R27+U27</f>
-        <v/>
-      </c>
-      <c r="Y27" s="10">
-        <f>M27+P27+S27+V27</f>
-        <v/>
-      </c>
-      <c r="AA27" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN27,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO27)</f>
+        <v/>
+      </c>
+      <c r="W27" s="9">
+        <f>U27-V27</f>
+        <v/>
+      </c>
+      <c r="X27" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN27,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO27)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO27,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO27)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN27,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO27)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN27,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO27)</f>
+        <v/>
+      </c>
+      <c r="AB27" s="9">
+        <f>Z27-AA27</f>
+        <v/>
+      </c>
+      <c r="AC27" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN27,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO27)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO27,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO27)</f>
+        <v/>
+      </c>
+      <c r="AE27" s="10">
+        <f>K27+P27+U27+Z27</f>
+        <v/>
+      </c>
+      <c r="AF27" s="10">
+        <f>L27+Q27+V27+AA27</f>
+        <v/>
+      </c>
+      <c r="AG27" s="10">
+        <f>M27+R27+W27+AB27</f>
+        <v/>
+      </c>
+      <c r="AH27" s="10">
+        <f>N27+S27+X27+AC27</f>
+        <v/>
+      </c>
+      <c r="AI27" s="10">
+        <f>O27+T27+Y27+AD27</f>
+        <v/>
+      </c>
+      <c r="AN27" s="8" t="n">
         <v>46062</v>
       </c>
-      <c r="AB27" s="8" t="n">
+      <c r="AO27" s="8" t="n">
         <v>46068</v>
       </c>
     </row>
@@ -3005,69 +3915,109 @@
         </is>
       </c>
       <c r="K28" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA28,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB28)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN28,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO28)</f>
         <v/>
       </c>
       <c r="L28" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA28,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB28)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN28,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO28)</f>
         <v/>
       </c>
       <c r="M28" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB28,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB28)</f>
+        <f>K28-L28</f>
         <v/>
       </c>
       <c r="N28" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA28,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB28)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN28,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO28)</f>
         <v/>
       </c>
       <c r="O28" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA28,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB28)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO28,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO28)</f>
         <v/>
       </c>
       <c r="P28" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB28,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB28)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN28,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO28)</f>
         <v/>
       </c>
       <c r="Q28" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA28,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB28)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN28,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO28)</f>
         <v/>
       </c>
       <c r="R28" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA28,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB28)</f>
+        <f>P28-Q28</f>
         <v/>
       </c>
       <c r="S28" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB28,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB28)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN28,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO28)</f>
         <v/>
       </c>
       <c r="T28" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA28,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB28)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO28,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO28)</f>
         <v/>
       </c>
       <c r="U28" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA28,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB28)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN28,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO28)</f>
         <v/>
       </c>
       <c r="V28" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB28,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB28)</f>
-        <v/>
-      </c>
-      <c r="W28" s="10">
-        <f>K28+N28+Q28+T28</f>
-        <v/>
-      </c>
-      <c r="X28" s="10">
-        <f>L28+O28+R28+U28</f>
-        <v/>
-      </c>
-      <c r="Y28" s="10">
-        <f>M28+P28+S28+V28</f>
-        <v/>
-      </c>
-      <c r="AA28" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN28,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO28)</f>
+        <v/>
+      </c>
+      <c r="W28" s="9">
+        <f>U28-V28</f>
+        <v/>
+      </c>
+      <c r="X28" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN28,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO28)</f>
+        <v/>
+      </c>
+      <c r="Y28" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO28,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO28)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN28,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO28)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN28,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO28)</f>
+        <v/>
+      </c>
+      <c r="AB28" s="9">
+        <f>Z28-AA28</f>
+        <v/>
+      </c>
+      <c r="AC28" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN28,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO28)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO28,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO28)</f>
+        <v/>
+      </c>
+      <c r="AE28" s="10">
+        <f>K28+P28+U28+Z28</f>
+        <v/>
+      </c>
+      <c r="AF28" s="10">
+        <f>L28+Q28+V28+AA28</f>
+        <v/>
+      </c>
+      <c r="AG28" s="10">
+        <f>M28+R28+W28+AB28</f>
+        <v/>
+      </c>
+      <c r="AH28" s="10">
+        <f>N28+S28+X28+AC28</f>
+        <v/>
+      </c>
+      <c r="AI28" s="10">
+        <f>O28+T28+Y28+AD28</f>
+        <v/>
+      </c>
+      <c r="AN28" s="8" t="n">
         <v>46069</v>
       </c>
-      <c r="AB28" s="8" t="n">
+      <c r="AO28" s="8" t="n">
         <v>46075</v>
       </c>
     </row>
@@ -3109,69 +4059,109 @@
         </is>
       </c>
       <c r="K29" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA29,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB29)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN29,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO29)</f>
         <v/>
       </c>
       <c r="L29" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA29,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB29)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN29,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO29)</f>
         <v/>
       </c>
       <c r="M29" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB29,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB29)</f>
+        <f>K29-L29</f>
         <v/>
       </c>
       <c r="N29" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA29,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB29)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN29,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO29)</f>
         <v/>
       </c>
       <c r="O29" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA29,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB29)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO29,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO29)</f>
         <v/>
       </c>
       <c r="P29" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB29,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB29)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN29,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO29)</f>
         <v/>
       </c>
       <c r="Q29" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA29,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB29)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN29,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO29)</f>
         <v/>
       </c>
       <c r="R29" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA29,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB29)</f>
+        <f>P29-Q29</f>
         <v/>
       </c>
       <c r="S29" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB29,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB29)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN29,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO29)</f>
         <v/>
       </c>
       <c r="T29" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA29,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB29)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO29,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO29)</f>
         <v/>
       </c>
       <c r="U29" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA29,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB29)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN29,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO29)</f>
         <v/>
       </c>
       <c r="V29" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB29,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB29)</f>
-        <v/>
-      </c>
-      <c r="W29" s="10">
-        <f>K29+N29+Q29+T29</f>
-        <v/>
-      </c>
-      <c r="X29" s="10">
-        <f>L29+O29+R29+U29</f>
-        <v/>
-      </c>
-      <c r="Y29" s="10">
-        <f>M29+P29+S29+V29</f>
-        <v/>
-      </c>
-      <c r="AA29" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN29,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO29)</f>
+        <v/>
+      </c>
+      <c r="W29" s="9">
+        <f>U29-V29</f>
+        <v/>
+      </c>
+      <c r="X29" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN29,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO29)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO29,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO29)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN29,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO29)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN29,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO29)</f>
+        <v/>
+      </c>
+      <c r="AB29" s="9">
+        <f>Z29-AA29</f>
+        <v/>
+      </c>
+      <c r="AC29" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN29,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO29)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO29,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO29)</f>
+        <v/>
+      </c>
+      <c r="AE29" s="10">
+        <f>K29+P29+U29+Z29</f>
+        <v/>
+      </c>
+      <c r="AF29" s="10">
+        <f>L29+Q29+V29+AA29</f>
+        <v/>
+      </c>
+      <c r="AG29" s="10">
+        <f>M29+R29+W29+AB29</f>
+        <v/>
+      </c>
+      <c r="AH29" s="10">
+        <f>N29+S29+X29+AC29</f>
+        <v/>
+      </c>
+      <c r="AI29" s="10">
+        <f>O29+T29+Y29+AD29</f>
+        <v/>
+      </c>
+      <c r="AN29" s="8" t="n">
         <v>46076</v>
       </c>
-      <c r="AB29" s="8" t="n">
+      <c r="AO29" s="8" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -3213,69 +4203,109 @@
         </is>
       </c>
       <c r="K30" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA30,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB30)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN30,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO30)</f>
         <v/>
       </c>
       <c r="L30" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA30,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB30)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN30,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO30)</f>
         <v/>
       </c>
       <c r="M30" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB30,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB30)</f>
+        <f>K30-L30</f>
         <v/>
       </c>
       <c r="N30" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA30,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB30)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN30,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO30)</f>
         <v/>
       </c>
       <c r="O30" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA30,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB30)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO30,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO30)</f>
         <v/>
       </c>
       <c r="P30" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB30,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB30)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN30,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO30)</f>
         <v/>
       </c>
       <c r="Q30" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA30,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB30)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN30,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO30)</f>
         <v/>
       </c>
       <c r="R30" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA30,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB30)</f>
+        <f>P30-Q30</f>
         <v/>
       </c>
       <c r="S30" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB30,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB30)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN30,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO30)</f>
         <v/>
       </c>
       <c r="T30" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA30,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB30)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO30,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO30)</f>
         <v/>
       </c>
       <c r="U30" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA30,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB30)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN30,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO30)</f>
         <v/>
       </c>
       <c r="V30" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB30,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB30)</f>
-        <v/>
-      </c>
-      <c r="W30" s="10">
-        <f>K30+N30+Q30+T30</f>
-        <v/>
-      </c>
-      <c r="X30" s="10">
-        <f>L30+O30+R30+U30</f>
-        <v/>
-      </c>
-      <c r="Y30" s="10">
-        <f>M30+P30+S30+V30</f>
-        <v/>
-      </c>
-      <c r="AA30" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN30,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO30)</f>
+        <v/>
+      </c>
+      <c r="W30" s="9">
+        <f>U30-V30</f>
+        <v/>
+      </c>
+      <c r="X30" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN30,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO30)</f>
+        <v/>
+      </c>
+      <c r="Y30" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO30,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO30)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN30,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO30)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN30,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO30)</f>
+        <v/>
+      </c>
+      <c r="AB30" s="9">
+        <f>Z30-AA30</f>
+        <v/>
+      </c>
+      <c r="AC30" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN30,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO30)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO30,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO30)</f>
+        <v/>
+      </c>
+      <c r="AE30" s="10">
+        <f>K30+P30+U30+Z30</f>
+        <v/>
+      </c>
+      <c r="AF30" s="10">
+        <f>L30+Q30+V30+AA30</f>
+        <v/>
+      </c>
+      <c r="AG30" s="10">
+        <f>M30+R30+W30+AB30</f>
+        <v/>
+      </c>
+      <c r="AH30" s="10">
+        <f>N30+S30+X30+AC30</f>
+        <v/>
+      </c>
+      <c r="AI30" s="10">
+        <f>O30+T30+Y30+AD30</f>
+        <v/>
+      </c>
+      <c r="AN30" s="8" t="n">
         <v>46083</v>
       </c>
-      <c r="AB30" s="8" t="n">
+      <c r="AO30" s="8" t="n">
         <v>46089</v>
       </c>
     </row>
@@ -3317,69 +4347,109 @@
         </is>
       </c>
       <c r="K31" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA31,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB31)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN31,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO31)</f>
         <v/>
       </c>
       <c r="L31" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA31,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB31)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN31,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO31)</f>
         <v/>
       </c>
       <c r="M31" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB31,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB31)</f>
+        <f>K31-L31</f>
         <v/>
       </c>
       <c r="N31" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA31,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB31)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN31,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO31)</f>
         <v/>
       </c>
       <c r="O31" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA31,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB31)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO31,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO31)</f>
         <v/>
       </c>
       <c r="P31" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB31,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB31)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN31,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO31)</f>
         <v/>
       </c>
       <c r="Q31" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA31,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB31)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN31,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO31)</f>
         <v/>
       </c>
       <c r="R31" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA31,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB31)</f>
+        <f>P31-Q31</f>
         <v/>
       </c>
       <c r="S31" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB31,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB31)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN31,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO31)</f>
         <v/>
       </c>
       <c r="T31" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA31,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB31)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO31,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO31)</f>
         <v/>
       </c>
       <c r="U31" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA31,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB31)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN31,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO31)</f>
         <v/>
       </c>
       <c r="V31" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB31,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB31)</f>
-        <v/>
-      </c>
-      <c r="W31" s="10">
-        <f>K31+N31+Q31+T31</f>
-        <v/>
-      </c>
-      <c r="X31" s="10">
-        <f>L31+O31+R31+U31</f>
-        <v/>
-      </c>
-      <c r="Y31" s="10">
-        <f>M31+P31+S31+V31</f>
-        <v/>
-      </c>
-      <c r="AA31" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN31,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO31)</f>
+        <v/>
+      </c>
+      <c r="W31" s="9">
+        <f>U31-V31</f>
+        <v/>
+      </c>
+      <c r="X31" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN31,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO31)</f>
+        <v/>
+      </c>
+      <c r="Y31" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO31,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO31)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN31,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO31)</f>
+        <v/>
+      </c>
+      <c r="AA31" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN31,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO31)</f>
+        <v/>
+      </c>
+      <c r="AB31" s="9">
+        <f>Z31-AA31</f>
+        <v/>
+      </c>
+      <c r="AC31" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN31,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO31)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO31,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO31)</f>
+        <v/>
+      </c>
+      <c r="AE31" s="10">
+        <f>K31+P31+U31+Z31</f>
+        <v/>
+      </c>
+      <c r="AF31" s="10">
+        <f>L31+Q31+V31+AA31</f>
+        <v/>
+      </c>
+      <c r="AG31" s="10">
+        <f>M31+R31+W31+AB31</f>
+        <v/>
+      </c>
+      <c r="AH31" s="10">
+        <f>N31+S31+X31+AC31</f>
+        <v/>
+      </c>
+      <c r="AI31" s="10">
+        <f>O31+T31+Y31+AD31</f>
+        <v/>
+      </c>
+      <c r="AN31" s="8" t="n">
         <v>46090</v>
       </c>
-      <c r="AB31" s="8" t="n">
+      <c r="AO31" s="8" t="n">
         <v>46096</v>
       </c>
     </row>
@@ -3421,69 +4491,109 @@
         </is>
       </c>
       <c r="K32" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA32,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB32)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN32,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO32)</f>
         <v/>
       </c>
       <c r="L32" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA32,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB32)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN32,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO32)</f>
         <v/>
       </c>
       <c r="M32" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB32,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB32)</f>
+        <f>K32-L32</f>
         <v/>
       </c>
       <c r="N32" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA32,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB32)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN32,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO32)</f>
         <v/>
       </c>
       <c r="O32" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA32,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB32)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO32,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO32)</f>
         <v/>
       </c>
       <c r="P32" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB32,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB32)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN32,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO32)</f>
         <v/>
       </c>
       <c r="Q32" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA32,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB32)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN32,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO32)</f>
         <v/>
       </c>
       <c r="R32" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA32,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB32)</f>
+        <f>P32-Q32</f>
         <v/>
       </c>
       <c r="S32" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB32,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB32)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN32,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO32)</f>
         <v/>
       </c>
       <c r="T32" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA32,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB32)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO32,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO32)</f>
         <v/>
       </c>
       <c r="U32" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA32,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB32)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN32,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO32)</f>
         <v/>
       </c>
       <c r="V32" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB32,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB32)</f>
-        <v/>
-      </c>
-      <c r="W32" s="10">
-        <f>K32+N32+Q32+T32</f>
-        <v/>
-      </c>
-      <c r="X32" s="10">
-        <f>L32+O32+R32+U32</f>
-        <v/>
-      </c>
-      <c r="Y32" s="10">
-        <f>M32+P32+S32+V32</f>
-        <v/>
-      </c>
-      <c r="AA32" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN32,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO32)</f>
+        <v/>
+      </c>
+      <c r="W32" s="9">
+        <f>U32-V32</f>
+        <v/>
+      </c>
+      <c r="X32" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN32,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO32)</f>
+        <v/>
+      </c>
+      <c r="Y32" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO32,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO32)</f>
+        <v/>
+      </c>
+      <c r="Z32" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN32,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO32)</f>
+        <v/>
+      </c>
+      <c r="AA32" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN32,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO32)</f>
+        <v/>
+      </c>
+      <c r="AB32" s="9">
+        <f>Z32-AA32</f>
+        <v/>
+      </c>
+      <c r="AC32" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN32,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO32)</f>
+        <v/>
+      </c>
+      <c r="AD32" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO32,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO32)</f>
+        <v/>
+      </c>
+      <c r="AE32" s="10">
+        <f>K32+P32+U32+Z32</f>
+        <v/>
+      </c>
+      <c r="AF32" s="10">
+        <f>L32+Q32+V32+AA32</f>
+        <v/>
+      </c>
+      <c r="AG32" s="10">
+        <f>M32+R32+W32+AB32</f>
+        <v/>
+      </c>
+      <c r="AH32" s="10">
+        <f>N32+S32+X32+AC32</f>
+        <v/>
+      </c>
+      <c r="AI32" s="10">
+        <f>O32+T32+Y32+AD32</f>
+        <v/>
+      </c>
+      <c r="AN32" s="8" t="n">
         <v>46097</v>
       </c>
-      <c r="AB32" s="8" t="n">
+      <c r="AO32" s="8" t="n">
         <v>46103</v>
       </c>
     </row>
@@ -3525,69 +4635,109 @@
         </is>
       </c>
       <c r="K33" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA33,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB33)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN33,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO33)</f>
         <v/>
       </c>
       <c r="L33" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA33,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB33)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN33,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO33)</f>
         <v/>
       </c>
       <c r="M33" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB33,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB33)</f>
+        <f>K33-L33</f>
         <v/>
       </c>
       <c r="N33" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA33,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB33)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN33,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO33)</f>
         <v/>
       </c>
       <c r="O33" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA33,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB33)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO33,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO33)</f>
         <v/>
       </c>
       <c r="P33" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB33,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB33)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN33,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO33)</f>
         <v/>
       </c>
       <c r="Q33" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA33,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB33)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN33,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO33)</f>
         <v/>
       </c>
       <c r="R33" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA33,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB33)</f>
+        <f>P33-Q33</f>
         <v/>
       </c>
       <c r="S33" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB33,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB33)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN33,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO33)</f>
         <v/>
       </c>
       <c r="T33" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA33,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB33)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO33,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO33)</f>
         <v/>
       </c>
       <c r="U33" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA33,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB33)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN33,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO33)</f>
         <v/>
       </c>
       <c r="V33" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB33,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB33)</f>
-        <v/>
-      </c>
-      <c r="W33" s="10">
-        <f>K33+N33+Q33+T33</f>
-        <v/>
-      </c>
-      <c r="X33" s="10">
-        <f>L33+O33+R33+U33</f>
-        <v/>
-      </c>
-      <c r="Y33" s="10">
-        <f>M33+P33+S33+V33</f>
-        <v/>
-      </c>
-      <c r="AA33" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN33,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO33)</f>
+        <v/>
+      </c>
+      <c r="W33" s="9">
+        <f>U33-V33</f>
+        <v/>
+      </c>
+      <c r="X33" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN33,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO33)</f>
+        <v/>
+      </c>
+      <c r="Y33" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO33,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO33)</f>
+        <v/>
+      </c>
+      <c r="Z33" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN33,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO33)</f>
+        <v/>
+      </c>
+      <c r="AA33" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN33,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO33)</f>
+        <v/>
+      </c>
+      <c r="AB33" s="9">
+        <f>Z33-AA33</f>
+        <v/>
+      </c>
+      <c r="AC33" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN33,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO33)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO33,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO33)</f>
+        <v/>
+      </c>
+      <c r="AE33" s="10">
+        <f>K33+P33+U33+Z33</f>
+        <v/>
+      </c>
+      <c r="AF33" s="10">
+        <f>L33+Q33+V33+AA33</f>
+        <v/>
+      </c>
+      <c r="AG33" s="10">
+        <f>M33+R33+W33+AB33</f>
+        <v/>
+      </c>
+      <c r="AH33" s="10">
+        <f>N33+S33+X33+AC33</f>
+        <v/>
+      </c>
+      <c r="AI33" s="10">
+        <f>O33+T33+Y33+AD33</f>
+        <v/>
+      </c>
+      <c r="AN33" s="8" t="n">
         <v>46104</v>
       </c>
-      <c r="AB33" s="8" t="n">
+      <c r="AO33" s="8" t="n">
         <v>46110</v>
       </c>
     </row>
@@ -3629,69 +4779,109 @@
         </is>
       </c>
       <c r="K34" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA34,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB34)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN34,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO34)</f>
         <v/>
       </c>
       <c r="L34" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA34,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB34)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN34,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO34)</f>
         <v/>
       </c>
       <c r="M34" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB34,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB34)</f>
+        <f>K34-L34</f>
         <v/>
       </c>
       <c r="N34" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA34,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB34)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN34,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO34)</f>
         <v/>
       </c>
       <c r="O34" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA34,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB34)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO34,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO34)</f>
         <v/>
       </c>
       <c r="P34" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB34,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB34)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN34,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO34)</f>
         <v/>
       </c>
       <c r="Q34" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA34,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB34)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN34,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO34)</f>
         <v/>
       </c>
       <c r="R34" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA34,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB34)</f>
+        <f>P34-Q34</f>
         <v/>
       </c>
       <c r="S34" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB34,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB34)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN34,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO34)</f>
         <v/>
       </c>
       <c r="T34" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA34,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB34)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO34,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO34)</f>
         <v/>
       </c>
       <c r="U34" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA34,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB34)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN34,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO34)</f>
         <v/>
       </c>
       <c r="V34" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB34,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB34)</f>
-        <v/>
-      </c>
-      <c r="W34" s="10">
-        <f>K34+N34+Q34+T34</f>
-        <v/>
-      </c>
-      <c r="X34" s="10">
-        <f>L34+O34+R34+U34</f>
-        <v/>
-      </c>
-      <c r="Y34" s="10">
-        <f>M34+P34+S34+V34</f>
-        <v/>
-      </c>
-      <c r="AA34" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN34,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO34)</f>
+        <v/>
+      </c>
+      <c r="W34" s="9">
+        <f>U34-V34</f>
+        <v/>
+      </c>
+      <c r="X34" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN34,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO34)</f>
+        <v/>
+      </c>
+      <c r="Y34" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO34,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO34)</f>
+        <v/>
+      </c>
+      <c r="Z34" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN34,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO34)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN34,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO34)</f>
+        <v/>
+      </c>
+      <c r="AB34" s="9">
+        <f>Z34-AA34</f>
+        <v/>
+      </c>
+      <c r="AC34" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN34,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO34)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO34,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO34)</f>
+        <v/>
+      </c>
+      <c r="AE34" s="10">
+        <f>K34+P34+U34+Z34</f>
+        <v/>
+      </c>
+      <c r="AF34" s="10">
+        <f>L34+Q34+V34+AA34</f>
+        <v/>
+      </c>
+      <c r="AG34" s="10">
+        <f>M34+R34+W34+AB34</f>
+        <v/>
+      </c>
+      <c r="AH34" s="10">
+        <f>N34+S34+X34+AC34</f>
+        <v/>
+      </c>
+      <c r="AI34" s="10">
+        <f>O34+T34+Y34+AD34</f>
+        <v/>
+      </c>
+      <c r="AN34" s="8" t="n">
         <v>46111</v>
       </c>
-      <c r="AB34" s="8" t="n">
+      <c r="AO34" s="8" t="n">
         <v>46117</v>
       </c>
     </row>
@@ -3733,69 +4923,109 @@
         </is>
       </c>
       <c r="K35" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA35,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB35)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN35,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO35)</f>
         <v/>
       </c>
       <c r="L35" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA35,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB35)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN35,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO35)</f>
         <v/>
       </c>
       <c r="M35" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB35,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB35)</f>
+        <f>K35-L35</f>
         <v/>
       </c>
       <c r="N35" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA35,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB35)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN35,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO35)</f>
         <v/>
       </c>
       <c r="O35" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA35,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB35)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO35,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO35)</f>
         <v/>
       </c>
       <c r="P35" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB35,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB35)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN35,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO35)</f>
         <v/>
       </c>
       <c r="Q35" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA35,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB35)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN35,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO35)</f>
         <v/>
       </c>
       <c r="R35" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA35,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB35)</f>
+        <f>P35-Q35</f>
         <v/>
       </c>
       <c r="S35" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB35,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB35)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN35,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO35)</f>
         <v/>
       </c>
       <c r="T35" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA35,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB35)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO35,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO35)</f>
         <v/>
       </c>
       <c r="U35" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA35,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB35)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN35,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO35)</f>
         <v/>
       </c>
       <c r="V35" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB35,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB35)</f>
-        <v/>
-      </c>
-      <c r="W35" s="10">
-        <f>K35+N35+Q35+T35</f>
-        <v/>
-      </c>
-      <c r="X35" s="10">
-        <f>L35+O35+R35+U35</f>
-        <v/>
-      </c>
-      <c r="Y35" s="10">
-        <f>M35+P35+S35+V35</f>
-        <v/>
-      </c>
-      <c r="AA35" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN35,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO35)</f>
+        <v/>
+      </c>
+      <c r="W35" s="9">
+        <f>U35-V35</f>
+        <v/>
+      </c>
+      <c r="X35" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN35,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO35)</f>
+        <v/>
+      </c>
+      <c r="Y35" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO35,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO35)</f>
+        <v/>
+      </c>
+      <c r="Z35" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN35,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO35)</f>
+        <v/>
+      </c>
+      <c r="AA35" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN35,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO35)</f>
+        <v/>
+      </c>
+      <c r="AB35" s="9">
+        <f>Z35-AA35</f>
+        <v/>
+      </c>
+      <c r="AC35" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN35,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO35)</f>
+        <v/>
+      </c>
+      <c r="AD35" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO35,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO35)</f>
+        <v/>
+      </c>
+      <c r="AE35" s="10">
+        <f>K35+P35+U35+Z35</f>
+        <v/>
+      </c>
+      <c r="AF35" s="10">
+        <f>L35+Q35+V35+AA35</f>
+        <v/>
+      </c>
+      <c r="AG35" s="10">
+        <f>M35+R35+W35+AB35</f>
+        <v/>
+      </c>
+      <c r="AH35" s="10">
+        <f>N35+S35+X35+AC35</f>
+        <v/>
+      </c>
+      <c r="AI35" s="10">
+        <f>O35+T35+Y35+AD35</f>
+        <v/>
+      </c>
+      <c r="AN35" s="8" t="n">
         <v>46118</v>
       </c>
-      <c r="AB35" s="8" t="n">
+      <c r="AO35" s="8" t="n">
         <v>46124</v>
       </c>
     </row>
@@ -3837,69 +5067,109 @@
         </is>
       </c>
       <c r="K36" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA36,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB36)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN36,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO36)</f>
         <v/>
       </c>
       <c r="L36" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA36,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB36)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN36,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO36)</f>
         <v/>
       </c>
       <c r="M36" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB36,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB36)</f>
+        <f>K36-L36</f>
         <v/>
       </c>
       <c r="N36" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA36,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB36)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN36,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO36)</f>
         <v/>
       </c>
       <c r="O36" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA36,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB36)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO36,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO36)</f>
         <v/>
       </c>
       <c r="P36" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB36,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB36)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN36,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO36)</f>
         <v/>
       </c>
       <c r="Q36" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA36,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB36)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN36,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO36)</f>
         <v/>
       </c>
       <c r="R36" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA36,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB36)</f>
+        <f>P36-Q36</f>
         <v/>
       </c>
       <c r="S36" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB36,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB36)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN36,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO36)</f>
         <v/>
       </c>
       <c r="T36" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA36,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB36)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO36,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO36)</f>
         <v/>
       </c>
       <c r="U36" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA36,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB36)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN36,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO36)</f>
         <v/>
       </c>
       <c r="V36" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB36,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB36)</f>
-        <v/>
-      </c>
-      <c r="W36" s="10">
-        <f>K36+N36+Q36+T36</f>
-        <v/>
-      </c>
-      <c r="X36" s="10">
-        <f>L36+O36+R36+U36</f>
-        <v/>
-      </c>
-      <c r="Y36" s="10">
-        <f>M36+P36+S36+V36</f>
-        <v/>
-      </c>
-      <c r="AA36" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN36,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO36)</f>
+        <v/>
+      </c>
+      <c r="W36" s="9">
+        <f>U36-V36</f>
+        <v/>
+      </c>
+      <c r="X36" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN36,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO36)</f>
+        <v/>
+      </c>
+      <c r="Y36" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO36,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO36)</f>
+        <v/>
+      </c>
+      <c r="Z36" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN36,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO36)</f>
+        <v/>
+      </c>
+      <c r="AA36" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN36,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO36)</f>
+        <v/>
+      </c>
+      <c r="AB36" s="9">
+        <f>Z36-AA36</f>
+        <v/>
+      </c>
+      <c r="AC36" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN36,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO36)</f>
+        <v/>
+      </c>
+      <c r="AD36" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO36,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO36)</f>
+        <v/>
+      </c>
+      <c r="AE36" s="10">
+        <f>K36+P36+U36+Z36</f>
+        <v/>
+      </c>
+      <c r="AF36" s="10">
+        <f>L36+Q36+V36+AA36</f>
+        <v/>
+      </c>
+      <c r="AG36" s="10">
+        <f>M36+R36+W36+AB36</f>
+        <v/>
+      </c>
+      <c r="AH36" s="10">
+        <f>N36+S36+X36+AC36</f>
+        <v/>
+      </c>
+      <c r="AI36" s="10">
+        <f>O36+T36+Y36+AD36</f>
+        <v/>
+      </c>
+      <c r="AN36" s="8" t="n">
         <v>46125</v>
       </c>
-      <c r="AB36" s="8" t="n">
+      <c r="AO36" s="8" t="n">
         <v>46131</v>
       </c>
     </row>
@@ -3941,69 +5211,109 @@
         </is>
       </c>
       <c r="K37" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA37,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB37)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN37,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO37)</f>
         <v/>
       </c>
       <c r="L37" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA37,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB37)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN37,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO37)</f>
         <v/>
       </c>
       <c r="M37" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB37,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB37)</f>
+        <f>K37-L37</f>
         <v/>
       </c>
       <c r="N37" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA37,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB37)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN37,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO37)</f>
         <v/>
       </c>
       <c r="O37" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA37,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB37)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO37,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO37)</f>
         <v/>
       </c>
       <c r="P37" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB37,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB37)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN37,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO37)</f>
         <v/>
       </c>
       <c r="Q37" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA37,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB37)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN37,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO37)</f>
         <v/>
       </c>
       <c r="R37" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA37,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB37)</f>
+        <f>P37-Q37</f>
         <v/>
       </c>
       <c r="S37" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB37,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB37)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN37,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO37)</f>
         <v/>
       </c>
       <c r="T37" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA37,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB37)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO37,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO37)</f>
         <v/>
       </c>
       <c r="U37" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA37,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB37)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN37,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO37)</f>
         <v/>
       </c>
       <c r="V37" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB37,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB37)</f>
-        <v/>
-      </c>
-      <c r="W37" s="10">
-        <f>K37+N37+Q37+T37</f>
-        <v/>
-      </c>
-      <c r="X37" s="10">
-        <f>L37+O37+R37+U37</f>
-        <v/>
-      </c>
-      <c r="Y37" s="10">
-        <f>M37+P37+S37+V37</f>
-        <v/>
-      </c>
-      <c r="AA37" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN37,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO37)</f>
+        <v/>
+      </c>
+      <c r="W37" s="9">
+        <f>U37-V37</f>
+        <v/>
+      </c>
+      <c r="X37" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN37,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO37)</f>
+        <v/>
+      </c>
+      <c r="Y37" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO37,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO37)</f>
+        <v/>
+      </c>
+      <c r="Z37" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN37,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO37)</f>
+        <v/>
+      </c>
+      <c r="AA37" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN37,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO37)</f>
+        <v/>
+      </c>
+      <c r="AB37" s="9">
+        <f>Z37-AA37</f>
+        <v/>
+      </c>
+      <c r="AC37" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN37,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO37)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO37,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO37)</f>
+        <v/>
+      </c>
+      <c r="AE37" s="10">
+        <f>K37+P37+U37+Z37</f>
+        <v/>
+      </c>
+      <c r="AF37" s="10">
+        <f>L37+Q37+V37+AA37</f>
+        <v/>
+      </c>
+      <c r="AG37" s="10">
+        <f>M37+R37+W37+AB37</f>
+        <v/>
+      </c>
+      <c r="AH37" s="10">
+        <f>N37+S37+X37+AC37</f>
+        <v/>
+      </c>
+      <c r="AI37" s="10">
+        <f>O37+T37+Y37+AD37</f>
+        <v/>
+      </c>
+      <c r="AN37" s="8" t="n">
         <v>46132</v>
       </c>
-      <c r="AB37" s="8" t="n">
+      <c r="AO37" s="8" t="n">
         <v>46138</v>
       </c>
     </row>
@@ -4045,69 +5355,109 @@
         </is>
       </c>
       <c r="K38" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA38,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB38)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN38,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO38)</f>
         <v/>
       </c>
       <c r="L38" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA38,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB38)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN38,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO38)</f>
         <v/>
       </c>
       <c r="M38" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB38,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB38)</f>
+        <f>K38-L38</f>
         <v/>
       </c>
       <c r="N38" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA38,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB38)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN38,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO38)</f>
         <v/>
       </c>
       <c r="O38" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA38,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB38)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO38,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO38)</f>
         <v/>
       </c>
       <c r="P38" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB38,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB38)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN38,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO38)</f>
         <v/>
       </c>
       <c r="Q38" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA38,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB38)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN38,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO38)</f>
         <v/>
       </c>
       <c r="R38" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA38,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB38)</f>
+        <f>P38-Q38</f>
         <v/>
       </c>
       <c r="S38" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB38,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB38)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN38,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO38)</f>
         <v/>
       </c>
       <c r="T38" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA38,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB38)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO38,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO38)</f>
         <v/>
       </c>
       <c r="U38" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA38,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB38)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN38,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO38)</f>
         <v/>
       </c>
       <c r="V38" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB38,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB38)</f>
-        <v/>
-      </c>
-      <c r="W38" s="10">
-        <f>K38+N38+Q38+T38</f>
-        <v/>
-      </c>
-      <c r="X38" s="10">
-        <f>L38+O38+R38+U38</f>
-        <v/>
-      </c>
-      <c r="Y38" s="10">
-        <f>M38+P38+S38+V38</f>
-        <v/>
-      </c>
-      <c r="AA38" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN38,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO38)</f>
+        <v/>
+      </c>
+      <c r="W38" s="9">
+        <f>U38-V38</f>
+        <v/>
+      </c>
+      <c r="X38" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN38,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO38)</f>
+        <v/>
+      </c>
+      <c r="Y38" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO38,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO38)</f>
+        <v/>
+      </c>
+      <c r="Z38" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN38,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO38)</f>
+        <v/>
+      </c>
+      <c r="AA38" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN38,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO38)</f>
+        <v/>
+      </c>
+      <c r="AB38" s="9">
+        <f>Z38-AA38</f>
+        <v/>
+      </c>
+      <c r="AC38" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN38,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO38)</f>
+        <v/>
+      </c>
+      <c r="AD38" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO38,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO38)</f>
+        <v/>
+      </c>
+      <c r="AE38" s="10">
+        <f>K38+P38+U38+Z38</f>
+        <v/>
+      </c>
+      <c r="AF38" s="10">
+        <f>L38+Q38+V38+AA38</f>
+        <v/>
+      </c>
+      <c r="AG38" s="10">
+        <f>M38+R38+W38+AB38</f>
+        <v/>
+      </c>
+      <c r="AH38" s="10">
+        <f>N38+S38+X38+AC38</f>
+        <v/>
+      </c>
+      <c r="AI38" s="10">
+        <f>O38+T38+Y38+AD38</f>
+        <v/>
+      </c>
+      <c r="AN38" s="8" t="n">
         <v>46139</v>
       </c>
-      <c r="AB38" s="8" t="n">
+      <c r="AO38" s="8" t="n">
         <v>46145</v>
       </c>
     </row>
@@ -4149,69 +5499,109 @@
         </is>
       </c>
       <c r="K39" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA39,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB39)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN39,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO39)</f>
         <v/>
       </c>
       <c r="L39" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA39,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB39)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN39,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO39)</f>
         <v/>
       </c>
       <c r="M39" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB39,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB39)</f>
+        <f>K39-L39</f>
         <v/>
       </c>
       <c r="N39" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA39,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB39)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN39,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO39)</f>
         <v/>
       </c>
       <c r="O39" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA39,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB39)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO39,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO39)</f>
         <v/>
       </c>
       <c r="P39" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB39,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB39)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN39,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO39)</f>
         <v/>
       </c>
       <c r="Q39" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA39,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB39)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN39,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO39)</f>
         <v/>
       </c>
       <c r="R39" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA39,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB39)</f>
+        <f>P39-Q39</f>
         <v/>
       </c>
       <c r="S39" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB39,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB39)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN39,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO39)</f>
         <v/>
       </c>
       <c r="T39" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA39,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB39)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO39,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO39)</f>
         <v/>
       </c>
       <c r="U39" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA39,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB39)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN39,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO39)</f>
         <v/>
       </c>
       <c r="V39" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB39,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB39)</f>
-        <v/>
-      </c>
-      <c r="W39" s="10">
-        <f>K39+N39+Q39+T39</f>
-        <v/>
-      </c>
-      <c r="X39" s="10">
-        <f>L39+O39+R39+U39</f>
-        <v/>
-      </c>
-      <c r="Y39" s="10">
-        <f>M39+P39+S39+V39</f>
-        <v/>
-      </c>
-      <c r="AA39" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN39,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO39)</f>
+        <v/>
+      </c>
+      <c r="W39" s="9">
+        <f>U39-V39</f>
+        <v/>
+      </c>
+      <c r="X39" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN39,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO39)</f>
+        <v/>
+      </c>
+      <c r="Y39" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO39,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO39)</f>
+        <v/>
+      </c>
+      <c r="Z39" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN39,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO39)</f>
+        <v/>
+      </c>
+      <c r="AA39" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN39,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO39)</f>
+        <v/>
+      </c>
+      <c r="AB39" s="9">
+        <f>Z39-AA39</f>
+        <v/>
+      </c>
+      <c r="AC39" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN39,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO39)</f>
+        <v/>
+      </c>
+      <c r="AD39" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO39,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO39)</f>
+        <v/>
+      </c>
+      <c r="AE39" s="10">
+        <f>K39+P39+U39+Z39</f>
+        <v/>
+      </c>
+      <c r="AF39" s="10">
+        <f>L39+Q39+V39+AA39</f>
+        <v/>
+      </c>
+      <c r="AG39" s="10">
+        <f>M39+R39+W39+AB39</f>
+        <v/>
+      </c>
+      <c r="AH39" s="10">
+        <f>N39+S39+X39+AC39</f>
+        <v/>
+      </c>
+      <c r="AI39" s="10">
+        <f>O39+T39+Y39+AD39</f>
+        <v/>
+      </c>
+      <c r="AN39" s="8" t="n">
         <v>46146</v>
       </c>
-      <c r="AB39" s="8" t="n">
+      <c r="AO39" s="8" t="n">
         <v>46152</v>
       </c>
     </row>
@@ -4253,69 +5643,109 @@
         </is>
       </c>
       <c r="K40" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA40,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB40)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN40,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO40)</f>
         <v/>
       </c>
       <c r="L40" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA40,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB40)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN40,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO40)</f>
         <v/>
       </c>
       <c r="M40" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB40,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB40)</f>
+        <f>K40-L40</f>
         <v/>
       </c>
       <c r="N40" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA40,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB40)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN40,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO40)</f>
         <v/>
       </c>
       <c r="O40" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA40,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB40)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO40,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO40)</f>
         <v/>
       </c>
       <c r="P40" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB40,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB40)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN40,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO40)</f>
         <v/>
       </c>
       <c r="Q40" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA40,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB40)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN40,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO40)</f>
         <v/>
       </c>
       <c r="R40" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA40,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB40)</f>
+        <f>P40-Q40</f>
         <v/>
       </c>
       <c r="S40" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB40,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB40)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN40,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO40)</f>
         <v/>
       </c>
       <c r="T40" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA40,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB40)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO40,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO40)</f>
         <v/>
       </c>
       <c r="U40" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA40,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB40)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN40,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO40)</f>
         <v/>
       </c>
       <c r="V40" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB40,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB40)</f>
-        <v/>
-      </c>
-      <c r="W40" s="10">
-        <f>K40+N40+Q40+T40</f>
-        <v/>
-      </c>
-      <c r="X40" s="10">
-        <f>L40+O40+R40+U40</f>
-        <v/>
-      </c>
-      <c r="Y40" s="10">
-        <f>M40+P40+S40+V40</f>
-        <v/>
-      </c>
-      <c r="AA40" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN40,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO40)</f>
+        <v/>
+      </c>
+      <c r="W40" s="9">
+        <f>U40-V40</f>
+        <v/>
+      </c>
+      <c r="X40" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN40,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO40)</f>
+        <v/>
+      </c>
+      <c r="Y40" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO40,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO40)</f>
+        <v/>
+      </c>
+      <c r="Z40" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN40,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO40)</f>
+        <v/>
+      </c>
+      <c r="AA40" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN40,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO40)</f>
+        <v/>
+      </c>
+      <c r="AB40" s="9">
+        <f>Z40-AA40</f>
+        <v/>
+      </c>
+      <c r="AC40" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN40,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO40)</f>
+        <v/>
+      </c>
+      <c r="AD40" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO40,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO40)</f>
+        <v/>
+      </c>
+      <c r="AE40" s="10">
+        <f>K40+P40+U40+Z40</f>
+        <v/>
+      </c>
+      <c r="AF40" s="10">
+        <f>L40+Q40+V40+AA40</f>
+        <v/>
+      </c>
+      <c r="AG40" s="10">
+        <f>M40+R40+W40+AB40</f>
+        <v/>
+      </c>
+      <c r="AH40" s="10">
+        <f>N40+S40+X40+AC40</f>
+        <v/>
+      </c>
+      <c r="AI40" s="10">
+        <f>O40+T40+Y40+AD40</f>
+        <v/>
+      </c>
+      <c r="AN40" s="8" t="n">
         <v>46153</v>
       </c>
-      <c r="AB40" s="8" t="n">
+      <c r="AO40" s="8" t="n">
         <v>46159</v>
       </c>
     </row>
@@ -4357,69 +5787,109 @@
         </is>
       </c>
       <c r="K41" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA41,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB41)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN41,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO41)</f>
         <v/>
       </c>
       <c r="L41" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA41,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB41)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN41,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO41)</f>
         <v/>
       </c>
       <c r="M41" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB41,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB41)</f>
+        <f>K41-L41</f>
         <v/>
       </c>
       <c r="N41" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA41,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB41)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN41,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO41)</f>
         <v/>
       </c>
       <c r="O41" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA41,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB41)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO41,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO41)</f>
         <v/>
       </c>
       <c r="P41" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB41,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB41)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN41,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO41)</f>
         <v/>
       </c>
       <c r="Q41" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA41,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB41)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN41,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO41)</f>
         <v/>
       </c>
       <c r="R41" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA41,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB41)</f>
+        <f>P41-Q41</f>
         <v/>
       </c>
       <c r="S41" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB41,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB41)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN41,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO41)</f>
         <v/>
       </c>
       <c r="T41" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA41,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB41)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO41,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO41)</f>
         <v/>
       </c>
       <c r="U41" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA41,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB41)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN41,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO41)</f>
         <v/>
       </c>
       <c r="V41" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB41,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB41)</f>
-        <v/>
-      </c>
-      <c r="W41" s="10">
-        <f>K41+N41+Q41+T41</f>
-        <v/>
-      </c>
-      <c r="X41" s="10">
-        <f>L41+O41+R41+U41</f>
-        <v/>
-      </c>
-      <c r="Y41" s="10">
-        <f>M41+P41+S41+V41</f>
-        <v/>
-      </c>
-      <c r="AA41" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN41,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO41)</f>
+        <v/>
+      </c>
+      <c r="W41" s="9">
+        <f>U41-V41</f>
+        <v/>
+      </c>
+      <c r="X41" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN41,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO41)</f>
+        <v/>
+      </c>
+      <c r="Y41" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO41,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO41)</f>
+        <v/>
+      </c>
+      <c r="Z41" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN41,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO41)</f>
+        <v/>
+      </c>
+      <c r="AA41" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN41,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO41)</f>
+        <v/>
+      </c>
+      <c r="AB41" s="9">
+        <f>Z41-AA41</f>
+        <v/>
+      </c>
+      <c r="AC41" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN41,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO41)</f>
+        <v/>
+      </c>
+      <c r="AD41" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO41,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO41)</f>
+        <v/>
+      </c>
+      <c r="AE41" s="10">
+        <f>K41+P41+U41+Z41</f>
+        <v/>
+      </c>
+      <c r="AF41" s="10">
+        <f>L41+Q41+V41+AA41</f>
+        <v/>
+      </c>
+      <c r="AG41" s="10">
+        <f>M41+R41+W41+AB41</f>
+        <v/>
+      </c>
+      <c r="AH41" s="10">
+        <f>N41+S41+X41+AC41</f>
+        <v/>
+      </c>
+      <c r="AI41" s="10">
+        <f>O41+T41+Y41+AD41</f>
+        <v/>
+      </c>
+      <c r="AN41" s="8" t="n">
         <v>46160</v>
       </c>
-      <c r="AB41" s="8" t="n">
+      <c r="AO41" s="8" t="n">
         <v>46166</v>
       </c>
     </row>
@@ -4461,69 +5931,109 @@
         </is>
       </c>
       <c r="K42" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA42,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB42)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN42,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO42)</f>
         <v/>
       </c>
       <c r="L42" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA42,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB42)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN42,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO42)</f>
         <v/>
       </c>
       <c r="M42" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB42,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB42)</f>
+        <f>K42-L42</f>
         <v/>
       </c>
       <c r="N42" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA42,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB42)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN42,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO42)</f>
         <v/>
       </c>
       <c r="O42" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA42,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB42)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO42,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO42)</f>
         <v/>
       </c>
       <c r="P42" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB42,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB42)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN42,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO42)</f>
         <v/>
       </c>
       <c r="Q42" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA42,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB42)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN42,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO42)</f>
         <v/>
       </c>
       <c r="R42" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA42,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB42)</f>
+        <f>P42-Q42</f>
         <v/>
       </c>
       <c r="S42" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB42,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB42)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN42,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO42)</f>
         <v/>
       </c>
       <c r="T42" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA42,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB42)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO42,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO42)</f>
         <v/>
       </c>
       <c r="U42" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA42,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB42)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN42,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO42)</f>
         <v/>
       </c>
       <c r="V42" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB42,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB42)</f>
-        <v/>
-      </c>
-      <c r="W42" s="10">
-        <f>K42+N42+Q42+T42</f>
-        <v/>
-      </c>
-      <c r="X42" s="10">
-        <f>L42+O42+R42+U42</f>
-        <v/>
-      </c>
-      <c r="Y42" s="10">
-        <f>M42+P42+S42+V42</f>
-        <v/>
-      </c>
-      <c r="AA42" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN42,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO42)</f>
+        <v/>
+      </c>
+      <c r="W42" s="9">
+        <f>U42-V42</f>
+        <v/>
+      </c>
+      <c r="X42" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN42,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO42)</f>
+        <v/>
+      </c>
+      <c r="Y42" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO42,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO42)</f>
+        <v/>
+      </c>
+      <c r="Z42" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN42,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO42)</f>
+        <v/>
+      </c>
+      <c r="AA42" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN42,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO42)</f>
+        <v/>
+      </c>
+      <c r="AB42" s="9">
+        <f>Z42-AA42</f>
+        <v/>
+      </c>
+      <c r="AC42" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN42,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO42)</f>
+        <v/>
+      </c>
+      <c r="AD42" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO42,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO42)</f>
+        <v/>
+      </c>
+      <c r="AE42" s="10">
+        <f>K42+P42+U42+Z42</f>
+        <v/>
+      </c>
+      <c r="AF42" s="10">
+        <f>L42+Q42+V42+AA42</f>
+        <v/>
+      </c>
+      <c r="AG42" s="10">
+        <f>M42+R42+W42+AB42</f>
+        <v/>
+      </c>
+      <c r="AH42" s="10">
+        <f>N42+S42+X42+AC42</f>
+        <v/>
+      </c>
+      <c r="AI42" s="10">
+        <f>O42+T42+Y42+AD42</f>
+        <v/>
+      </c>
+      <c r="AN42" s="8" t="n">
         <v>46167</v>
       </c>
-      <c r="AB42" s="8" t="n">
+      <c r="AO42" s="8" t="n">
         <v>46173</v>
       </c>
     </row>
@@ -4565,69 +6075,109 @@
         </is>
       </c>
       <c r="K43" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA43,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB43)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN43,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO43)</f>
         <v/>
       </c>
       <c r="L43" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA43,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB43)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN43,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO43)</f>
         <v/>
       </c>
       <c r="M43" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB43,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB43)</f>
+        <f>K43-L43</f>
         <v/>
       </c>
       <c r="N43" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA43,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB43)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN43,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO43)</f>
         <v/>
       </c>
       <c r="O43" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA43,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB43)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO43,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO43)</f>
         <v/>
       </c>
       <c r="P43" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB43,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB43)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN43,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO43)</f>
         <v/>
       </c>
       <c r="Q43" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA43,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB43)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN43,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO43)</f>
         <v/>
       </c>
       <c r="R43" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA43,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB43)</f>
+        <f>P43-Q43</f>
         <v/>
       </c>
       <c r="S43" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB43,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB43)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN43,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO43)</f>
         <v/>
       </c>
       <c r="T43" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA43,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB43)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO43,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO43)</f>
         <v/>
       </c>
       <c r="U43" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA43,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB43)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN43,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO43)</f>
         <v/>
       </c>
       <c r="V43" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB43,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB43)</f>
-        <v/>
-      </c>
-      <c r="W43" s="10">
-        <f>K43+N43+Q43+T43</f>
-        <v/>
-      </c>
-      <c r="X43" s="10">
-        <f>L43+O43+R43+U43</f>
-        <v/>
-      </c>
-      <c r="Y43" s="10">
-        <f>M43+P43+S43+V43</f>
-        <v/>
-      </c>
-      <c r="AA43" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN43,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO43)</f>
+        <v/>
+      </c>
+      <c r="W43" s="9">
+        <f>U43-V43</f>
+        <v/>
+      </c>
+      <c r="X43" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN43,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO43)</f>
+        <v/>
+      </c>
+      <c r="Y43" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO43,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO43)</f>
+        <v/>
+      </c>
+      <c r="Z43" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN43,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO43)</f>
+        <v/>
+      </c>
+      <c r="AA43" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN43,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO43)</f>
+        <v/>
+      </c>
+      <c r="AB43" s="9">
+        <f>Z43-AA43</f>
+        <v/>
+      </c>
+      <c r="AC43" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN43,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO43)</f>
+        <v/>
+      </c>
+      <c r="AD43" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO43,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO43)</f>
+        <v/>
+      </c>
+      <c r="AE43" s="10">
+        <f>K43+P43+U43+Z43</f>
+        <v/>
+      </c>
+      <c r="AF43" s="10">
+        <f>L43+Q43+V43+AA43</f>
+        <v/>
+      </c>
+      <c r="AG43" s="10">
+        <f>M43+R43+W43+AB43</f>
+        <v/>
+      </c>
+      <c r="AH43" s="10">
+        <f>N43+S43+X43+AC43</f>
+        <v/>
+      </c>
+      <c r="AI43" s="10">
+        <f>O43+T43+Y43+AD43</f>
+        <v/>
+      </c>
+      <c r="AN43" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="AB43" s="8" t="n">
+      <c r="AO43" s="8" t="n">
         <v>46180</v>
       </c>
     </row>
@@ -4669,69 +6219,109 @@
         </is>
       </c>
       <c r="K44" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA44,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB44)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN44,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO44)</f>
         <v/>
       </c>
       <c r="L44" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA44,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB44)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN44,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO44)</f>
         <v/>
       </c>
       <c r="M44" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB44,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB44)</f>
+        <f>K44-L44</f>
         <v/>
       </c>
       <c r="N44" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA44,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB44)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN44,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO44)</f>
         <v/>
       </c>
       <c r="O44" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA44,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB44)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO44,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO44)</f>
         <v/>
       </c>
       <c r="P44" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB44,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB44)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN44,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO44)</f>
         <v/>
       </c>
       <c r="Q44" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA44,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB44)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN44,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO44)</f>
         <v/>
       </c>
       <c r="R44" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA44,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB44)</f>
+        <f>P44-Q44</f>
         <v/>
       </c>
       <c r="S44" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB44,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB44)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN44,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO44)</f>
         <v/>
       </c>
       <c r="T44" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB44)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO44,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO44)</f>
         <v/>
       </c>
       <c r="U44" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA44,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB44)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN44,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO44)</f>
         <v/>
       </c>
       <c r="V44" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB44,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB44)</f>
-        <v/>
-      </c>
-      <c r="W44" s="10">
-        <f>K44+N44+Q44+T44</f>
-        <v/>
-      </c>
-      <c r="X44" s="10">
-        <f>L44+O44+R44+U44</f>
-        <v/>
-      </c>
-      <c r="Y44" s="10">
-        <f>M44+P44+S44+V44</f>
-        <v/>
-      </c>
-      <c r="AA44" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN44,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO44)</f>
+        <v/>
+      </c>
+      <c r="W44" s="9">
+        <f>U44-V44</f>
+        <v/>
+      </c>
+      <c r="X44" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN44,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO44)</f>
+        <v/>
+      </c>
+      <c r="Y44" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO44,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO44)</f>
+        <v/>
+      </c>
+      <c r="Z44" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO44)</f>
+        <v/>
+      </c>
+      <c r="AA44" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO44)</f>
+        <v/>
+      </c>
+      <c r="AB44" s="9">
+        <f>Z44-AA44</f>
+        <v/>
+      </c>
+      <c r="AC44" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN44,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO44)</f>
+        <v/>
+      </c>
+      <c r="AD44" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO44,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO44)</f>
+        <v/>
+      </c>
+      <c r="AE44" s="10">
+        <f>K44+P44+U44+Z44</f>
+        <v/>
+      </c>
+      <c r="AF44" s="10">
+        <f>L44+Q44+V44+AA44</f>
+        <v/>
+      </c>
+      <c r="AG44" s="10">
+        <f>M44+R44+W44+AB44</f>
+        <v/>
+      </c>
+      <c r="AH44" s="10">
+        <f>N44+S44+X44+AC44</f>
+        <v/>
+      </c>
+      <c r="AI44" s="10">
+        <f>O44+T44+Y44+AD44</f>
+        <v/>
+      </c>
+      <c r="AN44" s="8" t="n">
         <v>46181</v>
       </c>
-      <c r="AB44" s="8" t="n">
+      <c r="AO44" s="8" t="n">
         <v>46187</v>
       </c>
     </row>
@@ -4773,69 +6363,109 @@
         </is>
       </c>
       <c r="K45" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA45,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB45)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN45,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO45)</f>
         <v/>
       </c>
       <c r="L45" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA45,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB45)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN45,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO45)</f>
         <v/>
       </c>
       <c r="M45" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB45,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB45)</f>
+        <f>K45-L45</f>
         <v/>
       </c>
       <c r="N45" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA45,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB45)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN45,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO45)</f>
         <v/>
       </c>
       <c r="O45" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA45,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB45)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO45,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO45)</f>
         <v/>
       </c>
       <c r="P45" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB45,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB45)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN45,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO45)</f>
         <v/>
       </c>
       <c r="Q45" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA45,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB45)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN45,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO45)</f>
         <v/>
       </c>
       <c r="R45" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA45,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB45)</f>
+        <f>P45-Q45</f>
         <v/>
       </c>
       <c r="S45" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB45,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB45)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN45,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO45)</f>
         <v/>
       </c>
       <c r="T45" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA45,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB45)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO45,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO45)</f>
         <v/>
       </c>
       <c r="U45" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA45,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB45)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN45,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO45)</f>
         <v/>
       </c>
       <c r="V45" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB45,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB45)</f>
-        <v/>
-      </c>
-      <c r="W45" s="10">
-        <f>K45+N45+Q45+T45</f>
-        <v/>
-      </c>
-      <c r="X45" s="10">
-        <f>L45+O45+R45+U45</f>
-        <v/>
-      </c>
-      <c r="Y45" s="10">
-        <f>M45+P45+S45+V45</f>
-        <v/>
-      </c>
-      <c r="AA45" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN45,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO45)</f>
+        <v/>
+      </c>
+      <c r="W45" s="9">
+        <f>U45-V45</f>
+        <v/>
+      </c>
+      <c r="X45" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN45,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO45)</f>
+        <v/>
+      </c>
+      <c r="Y45" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO45,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO45)</f>
+        <v/>
+      </c>
+      <c r="Z45" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN45,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO45)</f>
+        <v/>
+      </c>
+      <c r="AA45" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN45,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO45)</f>
+        <v/>
+      </c>
+      <c r="AB45" s="9">
+        <f>Z45-AA45</f>
+        <v/>
+      </c>
+      <c r="AC45" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN45,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO45)</f>
+        <v/>
+      </c>
+      <c r="AD45" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO45,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO45)</f>
+        <v/>
+      </c>
+      <c r="AE45" s="10">
+        <f>K45+P45+U45+Z45</f>
+        <v/>
+      </c>
+      <c r="AF45" s="10">
+        <f>L45+Q45+V45+AA45</f>
+        <v/>
+      </c>
+      <c r="AG45" s="10">
+        <f>M45+R45+W45+AB45</f>
+        <v/>
+      </c>
+      <c r="AH45" s="10">
+        <f>N45+S45+X45+AC45</f>
+        <v/>
+      </c>
+      <c r="AI45" s="10">
+        <f>O45+T45+Y45+AD45</f>
+        <v/>
+      </c>
+      <c r="AN45" s="8" t="n">
         <v>46188</v>
       </c>
-      <c r="AB45" s="8" t="n">
+      <c r="AO45" s="8" t="n">
         <v>46194</v>
       </c>
     </row>
@@ -4877,69 +6507,109 @@
         </is>
       </c>
       <c r="K46" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA46,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB46)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN46,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO46)</f>
         <v/>
       </c>
       <c r="L46" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA46,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB46)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN46,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO46)</f>
         <v/>
       </c>
       <c r="M46" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB46,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB46)</f>
+        <f>K46-L46</f>
         <v/>
       </c>
       <c r="N46" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA46,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB46)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN46,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO46)</f>
         <v/>
       </c>
       <c r="O46" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA46,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB46)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO46,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO46)</f>
         <v/>
       </c>
       <c r="P46" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB46,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB46)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN46,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO46)</f>
         <v/>
       </c>
       <c r="Q46" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA46,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB46)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN46,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO46)</f>
         <v/>
       </c>
       <c r="R46" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA46,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB46)</f>
+        <f>P46-Q46</f>
         <v/>
       </c>
       <c r="S46" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB46,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB46)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN46,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO46)</f>
         <v/>
       </c>
       <c r="T46" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA46,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB46)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO46,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO46)</f>
         <v/>
       </c>
       <c r="U46" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA46,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB46)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN46,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO46)</f>
         <v/>
       </c>
       <c r="V46" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB46,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB46)</f>
-        <v/>
-      </c>
-      <c r="W46" s="10">
-        <f>K46+N46+Q46+T46</f>
-        <v/>
-      </c>
-      <c r="X46" s="10">
-        <f>L46+O46+R46+U46</f>
-        <v/>
-      </c>
-      <c r="Y46" s="10">
-        <f>M46+P46+S46+V46</f>
-        <v/>
-      </c>
-      <c r="AA46" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN46,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO46)</f>
+        <v/>
+      </c>
+      <c r="W46" s="9">
+        <f>U46-V46</f>
+        <v/>
+      </c>
+      <c r="X46" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN46,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO46)</f>
+        <v/>
+      </c>
+      <c r="Y46" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO46,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO46)</f>
+        <v/>
+      </c>
+      <c r="Z46" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN46,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO46)</f>
+        <v/>
+      </c>
+      <c r="AA46" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN46,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO46)</f>
+        <v/>
+      </c>
+      <c r="AB46" s="9">
+        <f>Z46-AA46</f>
+        <v/>
+      </c>
+      <c r="AC46" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN46,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO46)</f>
+        <v/>
+      </c>
+      <c r="AD46" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO46,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO46)</f>
+        <v/>
+      </c>
+      <c r="AE46" s="10">
+        <f>K46+P46+U46+Z46</f>
+        <v/>
+      </c>
+      <c r="AF46" s="10">
+        <f>L46+Q46+V46+AA46</f>
+        <v/>
+      </c>
+      <c r="AG46" s="10">
+        <f>M46+R46+W46+AB46</f>
+        <v/>
+      </c>
+      <c r="AH46" s="10">
+        <f>N46+S46+X46+AC46</f>
+        <v/>
+      </c>
+      <c r="AI46" s="10">
+        <f>O46+T46+Y46+AD46</f>
+        <v/>
+      </c>
+      <c r="AN46" s="8" t="n">
         <v>46195</v>
       </c>
-      <c r="AB46" s="8" t="n">
+      <c r="AO46" s="8" t="n">
         <v>46201</v>
       </c>
     </row>
@@ -4981,69 +6651,109 @@
         </is>
       </c>
       <c r="K47" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA47,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB47)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN47,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO47)</f>
         <v/>
       </c>
       <c r="L47" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA47,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB47)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN47,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO47)</f>
         <v/>
       </c>
       <c r="M47" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB47,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB47)</f>
+        <f>K47-L47</f>
         <v/>
       </c>
       <c r="N47" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA47,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB47)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN47,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO47)</f>
         <v/>
       </c>
       <c r="O47" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA47,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB47)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO47,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO47)</f>
         <v/>
       </c>
       <c r="P47" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB47,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB47)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN47,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO47)</f>
         <v/>
       </c>
       <c r="Q47" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA47,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB47)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN47,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO47)</f>
         <v/>
       </c>
       <c r="R47" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA47,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB47)</f>
+        <f>P47-Q47</f>
         <v/>
       </c>
       <c r="S47" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB47,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB47)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN47,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO47)</f>
         <v/>
       </c>
       <c r="T47" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA47,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB47)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO47,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO47)</f>
         <v/>
       </c>
       <c r="U47" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA47,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB47)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN47,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO47)</f>
         <v/>
       </c>
       <c r="V47" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB47,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB47)</f>
-        <v/>
-      </c>
-      <c r="W47" s="10">
-        <f>K47+N47+Q47+T47</f>
-        <v/>
-      </c>
-      <c r="X47" s="10">
-        <f>L47+O47+R47+U47</f>
-        <v/>
-      </c>
-      <c r="Y47" s="10">
-        <f>M47+P47+S47+V47</f>
-        <v/>
-      </c>
-      <c r="AA47" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN47,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO47)</f>
+        <v/>
+      </c>
+      <c r="W47" s="9">
+        <f>U47-V47</f>
+        <v/>
+      </c>
+      <c r="X47" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN47,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO47)</f>
+        <v/>
+      </c>
+      <c r="Y47" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO47,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO47)</f>
+        <v/>
+      </c>
+      <c r="Z47" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN47,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO47)</f>
+        <v/>
+      </c>
+      <c r="AA47" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN47,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO47)</f>
+        <v/>
+      </c>
+      <c r="AB47" s="9">
+        <f>Z47-AA47</f>
+        <v/>
+      </c>
+      <c r="AC47" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN47,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO47)</f>
+        <v/>
+      </c>
+      <c r="AD47" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO47,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO47)</f>
+        <v/>
+      </c>
+      <c r="AE47" s="10">
+        <f>K47+P47+U47+Z47</f>
+        <v/>
+      </c>
+      <c r="AF47" s="10">
+        <f>L47+Q47+V47+AA47</f>
+        <v/>
+      </c>
+      <c r="AG47" s="10">
+        <f>M47+R47+W47+AB47</f>
+        <v/>
+      </c>
+      <c r="AH47" s="10">
+        <f>N47+S47+X47+AC47</f>
+        <v/>
+      </c>
+      <c r="AI47" s="10">
+        <f>O47+T47+Y47+AD47</f>
+        <v/>
+      </c>
+      <c r="AN47" s="8" t="n">
         <v>46202</v>
       </c>
-      <c r="AB47" s="8" t="n">
+      <c r="AO47" s="8" t="n">
         <v>46208</v>
       </c>
     </row>
@@ -5085,69 +6795,109 @@
         </is>
       </c>
       <c r="K48" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA48,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB48)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN48,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO48)</f>
         <v/>
       </c>
       <c r="L48" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA48,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB48)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN48,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO48)</f>
         <v/>
       </c>
       <c r="M48" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB48,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB48)</f>
+        <f>K48-L48</f>
         <v/>
       </c>
       <c r="N48" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA48,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB48)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN48,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO48)</f>
         <v/>
       </c>
       <c r="O48" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA48,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB48)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO48,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO48)</f>
         <v/>
       </c>
       <c r="P48" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB48,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB48)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN48,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO48)</f>
         <v/>
       </c>
       <c r="Q48" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA48,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB48)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN48,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO48)</f>
         <v/>
       </c>
       <c r="R48" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA48,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB48)</f>
+        <f>P48-Q48</f>
         <v/>
       </c>
       <c r="S48" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB48,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB48)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN48,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO48)</f>
         <v/>
       </c>
       <c r="T48" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA48,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB48)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO48,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO48)</f>
         <v/>
       </c>
       <c r="U48" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA48,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB48)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN48,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO48)</f>
         <v/>
       </c>
       <c r="V48" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB48,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB48)</f>
-        <v/>
-      </c>
-      <c r="W48" s="10">
-        <f>K48+N48+Q48+T48</f>
-        <v/>
-      </c>
-      <c r="X48" s="10">
-        <f>L48+O48+R48+U48</f>
-        <v/>
-      </c>
-      <c r="Y48" s="10">
-        <f>M48+P48+S48+V48</f>
-        <v/>
-      </c>
-      <c r="AA48" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN48,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO48)</f>
+        <v/>
+      </c>
+      <c r="W48" s="9">
+        <f>U48-V48</f>
+        <v/>
+      </c>
+      <c r="X48" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN48,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO48)</f>
+        <v/>
+      </c>
+      <c r="Y48" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO48,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO48)</f>
+        <v/>
+      </c>
+      <c r="Z48" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN48,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO48)</f>
+        <v/>
+      </c>
+      <c r="AA48" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN48,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO48)</f>
+        <v/>
+      </c>
+      <c r="AB48" s="9">
+        <f>Z48-AA48</f>
+        <v/>
+      </c>
+      <c r="AC48" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN48,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO48)</f>
+        <v/>
+      </c>
+      <c r="AD48" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO48,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO48)</f>
+        <v/>
+      </c>
+      <c r="AE48" s="10">
+        <f>K48+P48+U48+Z48</f>
+        <v/>
+      </c>
+      <c r="AF48" s="10">
+        <f>L48+Q48+V48+AA48</f>
+        <v/>
+      </c>
+      <c r="AG48" s="10">
+        <f>M48+R48+W48+AB48</f>
+        <v/>
+      </c>
+      <c r="AH48" s="10">
+        <f>N48+S48+X48+AC48</f>
+        <v/>
+      </c>
+      <c r="AI48" s="10">
+        <f>O48+T48+Y48+AD48</f>
+        <v/>
+      </c>
+      <c r="AN48" s="8" t="n">
         <v>46209</v>
       </c>
-      <c r="AB48" s="8" t="n">
+      <c r="AO48" s="8" t="n">
         <v>46215</v>
       </c>
     </row>
@@ -5189,69 +6939,109 @@
         </is>
       </c>
       <c r="K49" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA49,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB49)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN49,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO49)</f>
         <v/>
       </c>
       <c r="L49" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA49,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB49)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN49,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO49)</f>
         <v/>
       </c>
       <c r="M49" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB49,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB49)</f>
+        <f>K49-L49</f>
         <v/>
       </c>
       <c r="N49" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA49,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB49)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN49,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO49)</f>
         <v/>
       </c>
       <c r="O49" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA49,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB49)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO49,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO49)</f>
         <v/>
       </c>
       <c r="P49" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB49,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB49)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN49,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO49)</f>
         <v/>
       </c>
       <c r="Q49" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA49,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB49)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN49,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO49)</f>
         <v/>
       </c>
       <c r="R49" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA49,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB49)</f>
+        <f>P49-Q49</f>
         <v/>
       </c>
       <c r="S49" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB49,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB49)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN49,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO49)</f>
         <v/>
       </c>
       <c r="T49" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA49,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB49)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO49,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO49)</f>
         <v/>
       </c>
       <c r="U49" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA49,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB49)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN49,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO49)</f>
         <v/>
       </c>
       <c r="V49" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB49,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB49)</f>
-        <v/>
-      </c>
-      <c r="W49" s="10">
-        <f>K49+N49+Q49+T49</f>
-        <v/>
-      </c>
-      <c r="X49" s="10">
-        <f>L49+O49+R49+U49</f>
-        <v/>
-      </c>
-      <c r="Y49" s="10">
-        <f>M49+P49+S49+V49</f>
-        <v/>
-      </c>
-      <c r="AA49" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN49,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO49)</f>
+        <v/>
+      </c>
+      <c r="W49" s="9">
+        <f>U49-V49</f>
+        <v/>
+      </c>
+      <c r="X49" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN49,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO49)</f>
+        <v/>
+      </c>
+      <c r="Y49" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO49,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO49)</f>
+        <v/>
+      </c>
+      <c r="Z49" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN49,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO49)</f>
+        <v/>
+      </c>
+      <c r="AA49" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN49,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO49)</f>
+        <v/>
+      </c>
+      <c r="AB49" s="9">
+        <f>Z49-AA49</f>
+        <v/>
+      </c>
+      <c r="AC49" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN49,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO49)</f>
+        <v/>
+      </c>
+      <c r="AD49" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO49,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO49)</f>
+        <v/>
+      </c>
+      <c r="AE49" s="10">
+        <f>K49+P49+U49+Z49</f>
+        <v/>
+      </c>
+      <c r="AF49" s="10">
+        <f>L49+Q49+V49+AA49</f>
+        <v/>
+      </c>
+      <c r="AG49" s="10">
+        <f>M49+R49+W49+AB49</f>
+        <v/>
+      </c>
+      <c r="AH49" s="10">
+        <f>N49+S49+X49+AC49</f>
+        <v/>
+      </c>
+      <c r="AI49" s="10">
+        <f>O49+T49+Y49+AD49</f>
+        <v/>
+      </c>
+      <c r="AN49" s="8" t="n">
         <v>46216</v>
       </c>
-      <c r="AB49" s="8" t="n">
+      <c r="AO49" s="8" t="n">
         <v>46222</v>
       </c>
     </row>
@@ -5293,69 +7083,109 @@
         </is>
       </c>
       <c r="K50" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA50,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB50)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN50,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO50)</f>
         <v/>
       </c>
       <c r="L50" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA50,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB50)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN50,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO50)</f>
         <v/>
       </c>
       <c r="M50" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB50,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB50)</f>
+        <f>K50-L50</f>
         <v/>
       </c>
       <c r="N50" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA50,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB50)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN50,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO50)</f>
         <v/>
       </c>
       <c r="O50" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA50,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB50)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO50,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO50)</f>
         <v/>
       </c>
       <c r="P50" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB50,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB50)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN50,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO50)</f>
         <v/>
       </c>
       <c r="Q50" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA50,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB50)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN50,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO50)</f>
         <v/>
       </c>
       <c r="R50" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA50,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB50)</f>
+        <f>P50-Q50</f>
         <v/>
       </c>
       <c r="S50" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB50,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB50)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN50,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO50)</f>
         <v/>
       </c>
       <c r="T50" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA50,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB50)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO50,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO50)</f>
         <v/>
       </c>
       <c r="U50" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA50,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB50)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN50,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO50)</f>
         <v/>
       </c>
       <c r="V50" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB50,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB50)</f>
-        <v/>
-      </c>
-      <c r="W50" s="10">
-        <f>K50+N50+Q50+T50</f>
-        <v/>
-      </c>
-      <c r="X50" s="10">
-        <f>L50+O50+R50+U50</f>
-        <v/>
-      </c>
-      <c r="Y50" s="10">
-        <f>M50+P50+S50+V50</f>
-        <v/>
-      </c>
-      <c r="AA50" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN50,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO50)</f>
+        <v/>
+      </c>
+      <c r="W50" s="9">
+        <f>U50-V50</f>
+        <v/>
+      </c>
+      <c r="X50" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN50,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO50)</f>
+        <v/>
+      </c>
+      <c r="Y50" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO50,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO50)</f>
+        <v/>
+      </c>
+      <c r="Z50" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN50,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO50)</f>
+        <v/>
+      </c>
+      <c r="AA50" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN50,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO50)</f>
+        <v/>
+      </c>
+      <c r="AB50" s="9">
+        <f>Z50-AA50</f>
+        <v/>
+      </c>
+      <c r="AC50" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN50,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO50)</f>
+        <v/>
+      </c>
+      <c r="AD50" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO50,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO50)</f>
+        <v/>
+      </c>
+      <c r="AE50" s="10">
+        <f>K50+P50+U50+Z50</f>
+        <v/>
+      </c>
+      <c r="AF50" s="10">
+        <f>L50+Q50+V50+AA50</f>
+        <v/>
+      </c>
+      <c r="AG50" s="10">
+        <f>M50+R50+W50+AB50</f>
+        <v/>
+      </c>
+      <c r="AH50" s="10">
+        <f>N50+S50+X50+AC50</f>
+        <v/>
+      </c>
+      <c r="AI50" s="10">
+        <f>O50+T50+Y50+AD50</f>
+        <v/>
+      </c>
+      <c r="AN50" s="8" t="n">
         <v>46223</v>
       </c>
-      <c r="AB50" s="8" t="n">
+      <c r="AO50" s="8" t="n">
         <v>46229</v>
       </c>
     </row>
@@ -5397,69 +7227,109 @@
         </is>
       </c>
       <c r="K51" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA51,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB51)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN51,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO51)</f>
         <v/>
       </c>
       <c r="L51" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA51,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB51)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN51,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO51)</f>
         <v/>
       </c>
       <c r="M51" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB51,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB51)</f>
+        <f>K51-L51</f>
         <v/>
       </c>
       <c r="N51" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA51,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB51)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN51,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO51)</f>
         <v/>
       </c>
       <c r="O51" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA51,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB51)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO51,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO51)</f>
         <v/>
       </c>
       <c r="P51" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB51,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB51)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN51,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO51)</f>
         <v/>
       </c>
       <c r="Q51" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA51,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB51)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN51,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO51)</f>
         <v/>
       </c>
       <c r="R51" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA51,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB51)</f>
+        <f>P51-Q51</f>
         <v/>
       </c>
       <c r="S51" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB51,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB51)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN51,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO51)</f>
         <v/>
       </c>
       <c r="T51" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA51,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB51)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO51,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO51)</f>
         <v/>
       </c>
       <c r="U51" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA51,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB51)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN51,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO51)</f>
         <v/>
       </c>
       <c r="V51" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB51,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB51)</f>
-        <v/>
-      </c>
-      <c r="W51" s="10">
-        <f>K51+N51+Q51+T51</f>
-        <v/>
-      </c>
-      <c r="X51" s="10">
-        <f>L51+O51+R51+U51</f>
-        <v/>
-      </c>
-      <c r="Y51" s="10">
-        <f>M51+P51+S51+V51</f>
-        <v/>
-      </c>
-      <c r="AA51" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN51,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO51)</f>
+        <v/>
+      </c>
+      <c r="W51" s="9">
+        <f>U51-V51</f>
+        <v/>
+      </c>
+      <c r="X51" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN51,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO51)</f>
+        <v/>
+      </c>
+      <c r="Y51" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO51,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO51)</f>
+        <v/>
+      </c>
+      <c r="Z51" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN51,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO51)</f>
+        <v/>
+      </c>
+      <c r="AA51" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN51,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO51)</f>
+        <v/>
+      </c>
+      <c r="AB51" s="9">
+        <f>Z51-AA51</f>
+        <v/>
+      </c>
+      <c r="AC51" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN51,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO51)</f>
+        <v/>
+      </c>
+      <c r="AD51" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO51,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO51)</f>
+        <v/>
+      </c>
+      <c r="AE51" s="10">
+        <f>K51+P51+U51+Z51</f>
+        <v/>
+      </c>
+      <c r="AF51" s="10">
+        <f>L51+Q51+V51+AA51</f>
+        <v/>
+      </c>
+      <c r="AG51" s="10">
+        <f>M51+R51+W51+AB51</f>
+        <v/>
+      </c>
+      <c r="AH51" s="10">
+        <f>N51+S51+X51+AC51</f>
+        <v/>
+      </c>
+      <c r="AI51" s="10">
+        <f>O51+T51+Y51+AD51</f>
+        <v/>
+      </c>
+      <c r="AN51" s="8" t="n">
         <v>46230</v>
       </c>
-      <c r="AB51" s="8" t="n">
+      <c r="AO51" s="8" t="n">
         <v>46236</v>
       </c>
     </row>
@@ -5501,69 +7371,109 @@
         </is>
       </c>
       <c r="K52" s="9">
-        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AA52,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB52)</f>
+        <f>SUMIFS('Adyen'!$B$11:$B$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN52,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO52)</f>
         <v/>
       </c>
       <c r="L52" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AA52,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AB52)</f>
+        <f>SUMIFS('Adyen'!$C$11:$C$207,'Adyen'!$A$11:$A$207,"&gt;="&amp;$AN52,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO52)</f>
         <v/>
       </c>
       <c r="M52" s="9">
-        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AB52,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AB52)</f>
+        <f>K52-L52</f>
         <v/>
       </c>
       <c r="N52" s="9">
-        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AA52,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB52)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$G$11:$G$207,"&gt;="&amp;$AN52,'Adyen'!$G$11:$G$207,"&lt;="&amp;$AO52)</f>
         <v/>
       </c>
       <c r="O52" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AA52,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AB52)</f>
+        <f>SUMIFS('Adyen'!$E$11:$E$207,'Adyen'!$A$11:$A$207,"&lt;="&amp;$AO52,'Adyen'!$G$11:$G$207,"&gt;"&amp;$AO52)</f>
         <v/>
       </c>
       <c r="P52" s="9">
-        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AB52,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AB52)</f>
+        <f>SUMIFS('Nuvei'!$B$11:$B$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN52,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO52)</f>
         <v/>
       </c>
       <c r="Q52" s="9">
-        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AA52,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB52)</f>
+        <f>SUMIFS('Nuvei'!$C$11:$C$296,'Nuvei'!$A$11:$A$296,"&gt;="&amp;$AN52,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO52)</f>
         <v/>
       </c>
       <c r="R52" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AA52,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AB52)</f>
+        <f>P52-Q52</f>
         <v/>
       </c>
       <c r="S52" s="9">
-        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AB52,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AB52)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$G$11:$G$296,"&gt;="&amp;$AN52,'Nuvei'!$G$11:$G$296,"&lt;="&amp;$AO52)</f>
         <v/>
       </c>
       <c r="T52" s="9">
-        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AA52,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB52)</f>
+        <f>SUMIFS('Nuvei'!$E$11:$E$296,'Nuvei'!$A$11:$A$296,"&lt;="&amp;$AO52,'Nuvei'!$G$11:$G$296,"&gt;"&amp;$AO52)</f>
         <v/>
       </c>
       <c r="U52" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AA52,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AB52)</f>
+        <f>SUMIFS('Shift4'!$B$11:$B$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN52,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO52)</f>
         <v/>
       </c>
       <c r="V52" s="9">
-        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AB52,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AB52)</f>
-        <v/>
-      </c>
-      <c r="W52" s="10">
-        <f>K52+N52+Q52+T52</f>
-        <v/>
-      </c>
-      <c r="X52" s="10">
-        <f>L52+O52+R52+U52</f>
-        <v/>
-      </c>
-      <c r="Y52" s="10">
-        <f>M52+P52+S52+V52</f>
-        <v/>
-      </c>
-      <c r="AA52" s="8" t="n">
+        <f>SUMIFS('Shift4'!$C$11:$C$116,'Shift4'!$A$11:$A$116,"&gt;="&amp;$AN52,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO52)</f>
+        <v/>
+      </c>
+      <c r="W52" s="9">
+        <f>U52-V52</f>
+        <v/>
+      </c>
+      <c r="X52" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$G$11:$G$116,"&gt;="&amp;$AN52,'Shift4'!$G$11:$G$116,"&lt;="&amp;$AO52)</f>
+        <v/>
+      </c>
+      <c r="Y52" s="9">
+        <f>SUMIFS('Shift4'!$E$11:$E$116,'Shift4'!$A$11:$A$116,"&lt;="&amp;$AO52,'Shift4'!$G$11:$G$116,"&gt;"&amp;$AO52)</f>
+        <v/>
+      </c>
+      <c r="Z52" s="9">
+        <f>SUMIFS('Paysafe'!$B$11:$B$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN52,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO52)</f>
+        <v/>
+      </c>
+      <c r="AA52" s="9">
+        <f>SUMIFS('Paysafe'!$C$11:$C$44,'Paysafe'!$A$11:$A$44,"&gt;="&amp;$AN52,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO52)</f>
+        <v/>
+      </c>
+      <c r="AB52" s="9">
+        <f>Z52-AA52</f>
+        <v/>
+      </c>
+      <c r="AC52" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$G$11:$G$44,"&gt;="&amp;$AN52,'Paysafe'!$G$11:$G$44,"&lt;="&amp;$AO52)</f>
+        <v/>
+      </c>
+      <c r="AD52" s="9">
+        <f>SUMIFS('Paysafe'!$E$11:$E$44,'Paysafe'!$A$11:$A$44,"&lt;="&amp;$AO52,'Paysafe'!$G$11:$G$44,"&gt;"&amp;$AO52)</f>
+        <v/>
+      </c>
+      <c r="AE52" s="10">
+        <f>K52+P52+U52+Z52</f>
+        <v/>
+      </c>
+      <c r="AF52" s="10">
+        <f>L52+Q52+V52+AA52</f>
+        <v/>
+      </c>
+      <c r="AG52" s="10">
+        <f>M52+R52+W52+AB52</f>
+        <v/>
+      </c>
+      <c r="AH52" s="10">
+        <f>N52+S52+X52+AC52</f>
+        <v/>
+      </c>
+      <c r="AI52" s="10">
+        <f>O52+T52+Y52+AD52</f>
+        <v/>
+      </c>
+      <c r="AN52" s="8" t="n">
         <v>46237</v>
       </c>
-      <c r="AB52" s="8" t="n">
+      <c r="AO52" s="8" t="n">
         <v>46243</v>
       </c>
     </row>
@@ -5618,7 +7528,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>→ Vendido = bruto vendido esa semana · Cobrado = neto liquidado realmente esa semana · Retenido = neto vendido hasta el domingo y aún sin liquidar.</t>
+          <t>→ Ventas = bruto vendido · Fees = comisiones · Venta Neta = Ventas−Fees · Collected = neto liquidado esa semana · Retenido = neto vendido hasta el domingo sin liquidar. (importes en €)</t>
         </is>
       </c>
     </row>
@@ -12326,12 +14236,12 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="Q5:S5"/>
     <mergeCell ref="J5:J6"/>
-    <mergeCell ref="T5:V5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="W5:Y5"/>
-    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="AE5:AI5"/>
+    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="Z5:AD5"/>
+    <mergeCell ref="P5:T5"/>
     <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
